--- a/Design-Files/DBS-Stepper-Module/BOM/Client_BOM  with Price.xlsx
+++ b/Design-Files/DBS-Stepper-Module/BOM/Client_BOM  with Price.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Iftikhar Ahmed\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\noelmcdermott-dbsdesign-hw\Design-Files\DBS-Stepper-Module\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="426">
   <si>
     <t>Component list</t>
   </si>
@@ -1185,9 +1185,6 @@
     <t>Remarks</t>
   </si>
   <si>
-    <t>Reviewer Remarks</t>
-  </si>
-  <si>
     <t>Value</t>
   </si>
   <si>
@@ -1288,6 +1285,18 @@
   </si>
   <si>
     <t>Chipsmall</t>
+  </si>
+  <si>
+    <t>Controlduino 01M21V00. Wideband lambda sensor control module for Arduino + rpm.</t>
+  </si>
+  <si>
+    <t>01M21V00</t>
+  </si>
+  <si>
+    <t>Controlduino</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Also Select optional parts  1# OEM : 0258017025.    2# AC/DC Power supply   </t>
   </si>
 </sst>
 </file>
@@ -1299,7 +1308,7 @@
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1317,13 +1326,6 @@
       <b/>
       <sz val="24"/>
       <color indexed="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color indexed="13"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -1418,13 +1420,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="10"/>
       <name val="Calibri"/>
@@ -1471,6 +1466,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -1498,7 +1501,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -1516,42 +1519,11 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
       <right/>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -1630,17 +1602,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -1669,158 +1630,143 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="15" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="3" borderId="9" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="3" borderId="6" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="20" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1845,60 +1791,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>1752600</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>161033</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch/>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="26222325" y="257175"/>
-          <a:ext cx="1714500" cy="1104008"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2165,7 +2057,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:S90"/>
+  <dimension ref="A1:R91"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="10" customWidth="1"/>
@@ -2185,10 +2077,9 @@
     <col min="16" max="16" width="19.7109375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="26.42578125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="26.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -2199,17 +2090,16 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="43"/>
-      <c r="L1" s="43"/>
-      <c r="M1" s="43"/>
-      <c r="N1" s="43"/>
-      <c r="O1" s="43"/>
-      <c r="P1" s="43"/>
-      <c r="Q1" s="43"/>
-      <c r="R1" s="43"/>
-      <c r="S1" s="44"/>
-    </row>
-    <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K1" s="48"/>
+      <c r="L1" s="48"/>
+      <c r="M1" s="48"/>
+      <c r="N1" s="48"/>
+      <c r="O1" s="48"/>
+      <c r="P1" s="48"/>
+      <c r="Q1" s="48"/>
+      <c r="R1" s="48"/>
+    </row>
+    <row r="2" spans="1:18" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="7"/>
       <c r="C2" s="13"/>
@@ -2217,112 +2107,107 @@
         <v>0</v>
       </c>
       <c r="E2" s="4"/>
-      <c r="F2" s="41" t="s">
-        <v>399</v>
+      <c r="F2" s="40" t="s">
+        <v>398</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="33"/>
-      <c r="L2" s="33"/>
-      <c r="M2" s="33"/>
-      <c r="N2" s="33"/>
-      <c r="O2" s="33"/>
-      <c r="P2" s="33"/>
-      <c r="Q2" s="33"/>
-      <c r="R2" s="33"/>
-      <c r="S2" s="47"/>
-    </row>
-    <row r="3" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I2" s="31"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="32"/>
+      <c r="P2" s="32"/>
+      <c r="Q2" s="32"/>
+      <c r="R2" s="32"/>
+    </row>
+    <row r="3" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="8"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="40" t="s">
+      <c r="C3" s="26"/>
+      <c r="D3" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="28"/>
-      <c r="F3" s="42" t="s">
-        <v>400</v>
-      </c>
-      <c r="G3" s="30"/>
-      <c r="H3" s="31"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="25"/>
-      <c r="K3" s="25"/>
-      <c r="L3" s="25"/>
-      <c r="M3" s="25"/>
-      <c r="N3" s="25"/>
-      <c r="O3" s="25"/>
-      <c r="P3" s="25"/>
-      <c r="Q3" s="25"/>
-      <c r="R3" s="25"/>
-      <c r="S3" s="48"/>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="E3" s="27"/>
+      <c r="F3" s="41" t="s">
+        <v>399</v>
+      </c>
+      <c r="G3" s="29"/>
+      <c r="H3" s="30"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="24"/>
+      <c r="K3" s="24"/>
+      <c r="L3" s="24"/>
+      <c r="M3" s="24"/>
+      <c r="N3" s="24"/>
+      <c r="O3" s="24"/>
+      <c r="P3" s="24"/>
+      <c r="Q3" s="24"/>
+      <c r="R3" s="24"/>
+    </row>
+    <row r="4" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="8"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="29"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
-      <c r="L4" s="25"/>
-      <c r="M4" s="25"/>
-      <c r="N4" s="25"/>
-      <c r="O4" s="25"/>
-      <c r="P4" s="25"/>
-      <c r="Q4" s="25"/>
-      <c r="R4" s="25"/>
-      <c r="S4" s="48"/>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="C4" s="26"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="24"/>
+      <c r="K4" s="24"/>
+      <c r="L4" s="24"/>
+      <c r="M4" s="24"/>
+      <c r="N4" s="24"/>
+      <c r="O4" s="24"/>
+      <c r="P4" s="24"/>
+      <c r="Q4" s="24"/>
+      <c r="R4" s="24"/>
+    </row>
+    <row r="5" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="9"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="35"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="35"/>
-      <c r="J5" s="36"/>
-      <c r="K5" s="36"/>
-      <c r="L5" s="36"/>
-      <c r="M5" s="36"/>
-      <c r="N5" s="36"/>
-      <c r="O5" s="36"/>
-      <c r="P5" s="36"/>
-      <c r="Q5" s="36"/>
-      <c r="R5" s="36"/>
-      <c r="S5" s="48"/>
-    </row>
-    <row r="6" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C5" s="33"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="35"/>
+      <c r="I5" s="34"/>
+      <c r="J5" s="35"/>
+      <c r="K5" s="35"/>
+      <c r="L5" s="35"/>
+      <c r="M5" s="35"/>
+      <c r="N5" s="35"/>
+      <c r="O5" s="35"/>
+      <c r="P5" s="35"/>
+      <c r="Q5" s="35"/>
+      <c r="R5" s="35"/>
+    </row>
+    <row r="6" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="11"/>
-      <c r="C6" s="37"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="29"/>
-      <c r="F6" s="38"/>
-      <c r="G6" s="35"/>
-      <c r="H6" s="36"/>
-      <c r="I6" s="35"/>
-      <c r="J6" s="36"/>
-      <c r="K6" s="36"/>
-      <c r="L6" s="36"/>
-      <c r="M6" s="36"/>
-      <c r="N6" s="36"/>
-      <c r="O6" s="36"/>
-      <c r="P6" s="36"/>
-      <c r="Q6" s="36"/>
-      <c r="R6" s="36"/>
-      <c r="S6" s="49"/>
-    </row>
-    <row r="7" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C6" s="36"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="37"/>
+      <c r="G6" s="34"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="34"/>
+      <c r="J6" s="35"/>
+      <c r="K6" s="35"/>
+      <c r="L6" s="35"/>
+      <c r="M6" s="35"/>
+      <c r="N6" s="35"/>
+      <c r="O6" s="35"/>
+      <c r="P6" s="35"/>
+      <c r="Q6" s="35"/>
+      <c r="R6" s="35"/>
+    </row>
+    <row r="7" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="12" t="s">
         <v>2</v>
@@ -2352,40 +2237,37 @@
         <v>296</v>
       </c>
       <c r="K7" s="12" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L7" s="12" t="s">
         <v>384</v>
       </c>
       <c r="M7" s="12" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="N7" s="12" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="O7" s="12" t="s">
         <v>386</v>
       </c>
       <c r="P7" s="12" t="s">
+        <v>390</v>
+      </c>
+      <c r="Q7" s="12" t="s">
         <v>391</v>
-      </c>
-      <c r="Q7" s="12" t="s">
-        <v>392</v>
       </c>
       <c r="R7" s="12" t="s">
         <v>387</v>
       </c>
-      <c r="S7" s="12" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:18" ht="36" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="16">
         <f>ROW(B8) - ROW($B$7)</f>
         <v>1</v>
       </c>
-      <c r="C8" s="23" t="s">
+      <c r="C8" s="22" t="s">
         <v>6</v>
       </c>
       <c r="D8" s="14" t="s">
@@ -2404,7 +2286,7 @@
         <v>266</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="J8" s="14" t="s">
         <v>297</v>
@@ -2422,82 +2304,80 @@
       <c r="N8" s="14">
         <v>300</v>
       </c>
-      <c r="O8" s="51" t="s">
-        <v>403</v>
+      <c r="O8" s="43" t="s">
+        <v>402</v>
       </c>
       <c r="P8" s="15">
         <v>3.3E-3</v>
       </c>
       <c r="Q8" s="15">
-        <f>P8*N8</f>
+        <f t="shared" ref="Q8:Q43" si="0">P8*N8</f>
         <v>0.99</v>
       </c>
       <c r="R8" s="14"/>
-      <c r="S8" s="20"/>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="17">
-        <f t="shared" ref="B9:B76" si="0">ROW(B9) - ROW($B$7)</f>
+        <f t="shared" ref="B9:B77" si="1">ROW(B9) - ROW($B$7)</f>
         <v>2</v>
       </c>
-      <c r="C9" s="24" t="s">
+      <c r="C9" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="21" t="s">
+      <c r="D9" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="E9" s="21" t="s">
+      <c r="E9" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="F9" s="21" t="s">
+      <c r="F9" s="20" t="s">
         <v>171</v>
       </c>
-      <c r="G9" s="21" t="s">
+      <c r="G9" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="H9" s="21" t="s">
+      <c r="H9" s="20" t="s">
         <v>266</v>
       </c>
-      <c r="I9" s="21" t="s">
-        <v>397</v>
-      </c>
-      <c r="J9" s="21" t="s">
+      <c r="I9" s="20" t="s">
+        <v>396</v>
+      </c>
+      <c r="J9" s="20" t="s">
         <v>298</v>
       </c>
-      <c r="K9" s="21" t="s">
+      <c r="K9" s="20" t="s">
         <v>353</v>
       </c>
-      <c r="L9" s="21">
+      <c r="L9" s="20">
         <v>2</v>
       </c>
       <c r="M9" s="14">
-        <f t="shared" ref="M9:M72" si="1">L9*10</f>
+        <f t="shared" ref="M9:M72" si="2">L9*10</f>
         <v>20</v>
       </c>
-      <c r="N9" s="21">
+      <c r="N9" s="20">
         <v>25</v>
       </c>
-      <c r="O9" s="52" t="s">
-        <v>403</v>
-      </c>
-      <c r="P9" s="22">
+      <c r="O9" s="44" t="s">
+        <v>402</v>
+      </c>
+      <c r="P9" s="21">
         <v>9.8900000000000002E-2</v>
       </c>
-      <c r="Q9" s="22">
-        <f>P9*N9</f>
+      <c r="Q9" s="21">
+        <f t="shared" si="0"/>
         <v>2.4725000000000001</v>
       </c>
-      <c r="R9" s="21"/>
-      <c r="S9" s="21"/>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R9" s="20"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="16">
         <f>ROW(B10) - ROW($B$7)</f>
         <v>3</v>
       </c>
-      <c r="C10" s="23" t="s">
+      <c r="C10" s="22" t="s">
         <v>7</v>
       </c>
       <c r="D10" s="14" t="s">
@@ -2509,17 +2389,17 @@
       <c r="F10" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="G10" s="50" t="s">
+      <c r="G10" s="42" t="s">
         <v>215</v>
       </c>
       <c r="H10" s="14" t="s">
         <v>267</v>
       </c>
       <c r="I10" s="14" t="s">
+        <v>408</v>
+      </c>
+      <c r="J10" s="14" t="s">
         <v>409</v>
-      </c>
-      <c r="J10" s="14" t="s">
-        <v>410</v>
       </c>
       <c r="K10" s="14" t="s">
         <v>354</v>
@@ -2528,88 +2408,86 @@
         <v>1</v>
       </c>
       <c r="M10" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="N10" s="14">
         <v>100</v>
       </c>
-      <c r="O10" s="51" t="s">
-        <v>403</v>
+      <c r="O10" s="43" t="s">
+        <v>402</v>
       </c>
       <c r="P10" s="15">
         <v>2.8E-3</v>
       </c>
       <c r="Q10" s="15">
-        <f>P10*N10</f>
+        <f t="shared" si="0"/>
         <v>0.27999999999999997</v>
       </c>
       <c r="R10" s="14"/>
-      <c r="S10" s="20"/>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="17">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="C11" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F11" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>216</v>
+      </c>
+      <c r="H11" s="20" t="s">
+        <v>268</v>
+      </c>
+      <c r="I11" s="20" t="s">
+        <v>396</v>
+      </c>
+      <c r="J11" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="K11" s="20" t="s">
+        <v>355</v>
+      </c>
+      <c r="L11" s="20">
+        <v>3</v>
+      </c>
+      <c r="M11" s="14">
+        <f t="shared" si="2"/>
+        <v>30</v>
+      </c>
+      <c r="N11" s="20">
+        <v>30</v>
+      </c>
+      <c r="O11" s="44" t="s">
+        <v>402</v>
+      </c>
+      <c r="P11" s="21">
+        <v>0.2868</v>
+      </c>
+      <c r="Q11" s="21">
         <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="C11" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E11" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="F11" s="21" t="s">
-        <v>171</v>
-      </c>
-      <c r="G11" s="21" t="s">
-        <v>216</v>
-      </c>
-      <c r="H11" s="21" t="s">
-        <v>268</v>
-      </c>
-      <c r="I11" s="21" t="s">
-        <v>397</v>
-      </c>
-      <c r="J11" s="21" t="s">
-        <v>299</v>
-      </c>
-      <c r="K11" s="21" t="s">
-        <v>355</v>
-      </c>
-      <c r="L11" s="21">
-        <v>3</v>
-      </c>
-      <c r="M11" s="14">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="N11" s="21">
-        <v>30</v>
-      </c>
-      <c r="O11" s="52" t="s">
-        <v>403</v>
-      </c>
-      <c r="P11" s="22">
-        <v>0.2868</v>
-      </c>
-      <c r="Q11" s="22">
-        <f>P11*N11</f>
         <v>8.6039999999999992</v>
       </c>
-      <c r="R11" s="21"/>
-      <c r="S11" s="21"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R11" s="20"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="16">
         <f>ROW(B12) - ROW($B$7)</f>
         <v>5</v>
       </c>
-      <c r="C12" s="23" t="s">
+      <c r="C12" s="22" t="s">
         <v>6</v>
       </c>
       <c r="D12" s="14" t="s">
@@ -2628,7 +2506,7 @@
         <v>266</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="J12" s="14" t="s">
         <v>300</v>
@@ -2640,88 +2518,86 @@
         <v>1</v>
       </c>
       <c r="M12" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="N12" s="14">
         <v>100</v>
       </c>
-      <c r="O12" s="51" t="s">
-        <v>403</v>
+      <c r="O12" s="43" t="s">
+        <v>402</v>
       </c>
       <c r="P12" s="15">
         <v>2.0999999999999999E-3</v>
       </c>
       <c r="Q12" s="15">
-        <f>P12*N12</f>
+        <f t="shared" si="0"/>
         <v>0.21</v>
       </c>
       <c r="R12" s="14"/>
-      <c r="S12" s="20"/>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="17">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="C13" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="F13" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>218</v>
+      </c>
+      <c r="H13" s="20" t="s">
+        <v>269</v>
+      </c>
+      <c r="I13" s="20" t="s">
+        <v>396</v>
+      </c>
+      <c r="J13" s="20" t="s">
+        <v>301</v>
+      </c>
+      <c r="K13" s="20" t="s">
+        <v>357</v>
+      </c>
+      <c r="L13" s="20">
+        <v>3</v>
+      </c>
+      <c r="M13" s="14">
+        <f t="shared" si="2"/>
+        <v>30</v>
+      </c>
+      <c r="N13" s="20">
+        <v>100</v>
+      </c>
+      <c r="O13" s="44" t="s">
+        <v>402</v>
+      </c>
+      <c r="P13" s="21">
+        <v>4.4999999999999997E-3</v>
+      </c>
+      <c r="Q13" s="21">
         <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="C13" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="D13" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="E13" s="21" t="s">
-        <v>106</v>
-      </c>
-      <c r="F13" s="21" t="s">
-        <v>170</v>
-      </c>
-      <c r="G13" s="21" t="s">
-        <v>218</v>
-      </c>
-      <c r="H13" s="21" t="s">
-        <v>269</v>
-      </c>
-      <c r="I13" s="21" t="s">
-        <v>397</v>
-      </c>
-      <c r="J13" s="21" t="s">
-        <v>301</v>
-      </c>
-      <c r="K13" s="21" t="s">
-        <v>357</v>
-      </c>
-      <c r="L13" s="21">
-        <v>3</v>
-      </c>
-      <c r="M13" s="14">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="N13" s="21">
-        <v>100</v>
-      </c>
-      <c r="O13" s="52" t="s">
-        <v>403</v>
-      </c>
-      <c r="P13" s="22">
-        <v>4.4999999999999997E-3</v>
-      </c>
-      <c r="Q13" s="22">
-        <f>P13*N13</f>
         <v>0.44999999999999996</v>
       </c>
-      <c r="R13" s="21"/>
-      <c r="S13" s="21"/>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R13" s="20"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="16">
         <f>ROW(B14) - ROW($B$7)</f>
         <v>7</v>
       </c>
-      <c r="C14" s="23" t="s">
+      <c r="C14" s="22" t="s">
         <v>6</v>
       </c>
       <c r="D14" s="14" t="s">
@@ -2733,17 +2609,17 @@
       <c r="F14" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="G14" s="50" t="s">
+      <c r="G14" s="42" t="s">
         <v>219</v>
       </c>
       <c r="H14" s="14" t="s">
         <v>266</v>
       </c>
       <c r="I14" s="14" t="s">
+        <v>400</v>
+      </c>
+      <c r="J14" s="14" t="s">
         <v>401</v>
-      </c>
-      <c r="J14" s="14" t="s">
-        <v>402</v>
       </c>
       <c r="K14" s="14" t="s">
         <v>358</v>
@@ -2752,88 +2628,86 @@
         <v>1</v>
       </c>
       <c r="M14" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="N14" s="14">
         <v>50</v>
       </c>
-      <c r="O14" s="51" t="s">
-        <v>403</v>
+      <c r="O14" s="43" t="s">
+        <v>402</v>
       </c>
       <c r="P14" s="15">
         <v>9.2999999999999992E-3</v>
       </c>
       <c r="Q14" s="15">
-        <f>P14*N14</f>
+        <f t="shared" si="0"/>
         <v>0.46499999999999997</v>
       </c>
       <c r="R14" s="14"/>
-      <c r="S14" s="20"/>
-    </row>
-    <row r="15" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:18" ht="36" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="17">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="C15" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="F15" s="20" t="s">
+        <v>403</v>
+      </c>
+      <c r="G15" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="H15" s="20" t="s">
+        <v>270</v>
+      </c>
+      <c r="I15" s="20" t="s">
+        <v>396</v>
+      </c>
+      <c r="J15" s="20" t="s">
+        <v>302</v>
+      </c>
+      <c r="K15" s="20" t="s">
+        <v>355</v>
+      </c>
+      <c r="L15" s="20">
+        <v>1</v>
+      </c>
+      <c r="M15" s="14">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="N15" s="20">
+        <v>20</v>
+      </c>
+      <c r="O15" s="44" t="s">
+        <v>402</v>
+      </c>
+      <c r="P15" s="21">
+        <v>3.2899999999999999E-2</v>
+      </c>
+      <c r="Q15" s="21">
         <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="C15" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="D15" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="E15" s="21" t="s">
-        <v>108</v>
-      </c>
-      <c r="F15" s="21" t="s">
-        <v>404</v>
-      </c>
-      <c r="G15" s="21" t="s">
-        <v>173</v>
-      </c>
-      <c r="H15" s="21" t="s">
-        <v>270</v>
-      </c>
-      <c r="I15" s="21" t="s">
-        <v>397</v>
-      </c>
-      <c r="J15" s="21" t="s">
-        <v>302</v>
-      </c>
-      <c r="K15" s="21" t="s">
-        <v>355</v>
-      </c>
-      <c r="L15" s="21">
-        <v>1</v>
-      </c>
-      <c r="M15" s="14">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="N15" s="21">
-        <v>20</v>
-      </c>
-      <c r="O15" s="52" t="s">
-        <v>403</v>
-      </c>
-      <c r="P15" s="22">
-        <v>3.2899999999999999E-2</v>
-      </c>
-      <c r="Q15" s="22">
-        <f>P15*N15</f>
         <v>0.65799999999999992</v>
       </c>
-      <c r="R15" s="21"/>
-      <c r="S15" s="21"/>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R15" s="20"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="16">
         <f>ROW(B16) - ROW($B$7)</f>
         <v>9</v>
       </c>
-      <c r="C16" s="24" t="s">
+      <c r="C16" s="23" t="s">
         <v>6</v>
       </c>
       <c r="D16" s="14" t="s">
@@ -2845,17 +2719,17 @@
       <c r="F16" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="G16" s="50" t="s">
+      <c r="G16" s="42" t="s">
         <v>220</v>
       </c>
       <c r="H16" s="14" t="s">
         <v>266</v>
       </c>
       <c r="I16" s="14" t="s">
+        <v>404</v>
+      </c>
+      <c r="J16" s="14" t="s">
         <v>405</v>
-      </c>
-      <c r="J16" s="14" t="s">
-        <v>406</v>
       </c>
       <c r="K16" s="14" t="s">
         <v>359</v>
@@ -2864,88 +2738,86 @@
         <v>2</v>
       </c>
       <c r="M16" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="N16" s="14">
         <v>50</v>
       </c>
-      <c r="O16" s="51" t="s">
-        <v>403</v>
+      <c r="O16" s="43" t="s">
+        <v>402</v>
       </c>
       <c r="P16" s="15">
         <v>1.26E-2</v>
       </c>
       <c r="Q16" s="15">
-        <f>P16*N16</f>
+        <f t="shared" si="0"/>
         <v>0.63</v>
       </c>
       <c r="R16" s="14"/>
-      <c r="S16" s="20"/>
-    </row>
-    <row r="17" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:18" ht="36" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="17">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="C17" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="D17" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="F17" s="20" t="s">
+        <v>403</v>
+      </c>
+      <c r="G17" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="H17" s="20" t="s">
+        <v>270</v>
+      </c>
+      <c r="I17" s="20" t="s">
+        <v>396</v>
+      </c>
+      <c r="J17" s="20" t="s">
+        <v>303</v>
+      </c>
+      <c r="K17" s="20" t="s">
+        <v>360</v>
+      </c>
+      <c r="L17" s="20">
+        <v>2</v>
+      </c>
+      <c r="M17" s="14">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="N17" s="20">
+        <v>30</v>
+      </c>
+      <c r="O17" s="44" t="s">
+        <v>402</v>
+      </c>
+      <c r="P17" s="21">
+        <v>5.7099999999999998E-2</v>
+      </c>
+      <c r="Q17" s="21">
         <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="C17" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="D17" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="E17" s="21" t="s">
-        <v>110</v>
-      </c>
-      <c r="F17" s="21" t="s">
-        <v>404</v>
-      </c>
-      <c r="G17" s="21" t="s">
-        <v>174</v>
-      </c>
-      <c r="H17" s="21" t="s">
-        <v>270</v>
-      </c>
-      <c r="I17" s="21" t="s">
-        <v>397</v>
-      </c>
-      <c r="J17" s="21" t="s">
-        <v>303</v>
-      </c>
-      <c r="K17" s="21" t="s">
-        <v>360</v>
-      </c>
-      <c r="L17" s="21">
-        <v>2</v>
-      </c>
-      <c r="M17" s="14">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="N17" s="21">
-        <v>30</v>
-      </c>
-      <c r="O17" s="52" t="s">
-        <v>403</v>
-      </c>
-      <c r="P17" s="22">
-        <v>5.7099999999999998E-2</v>
-      </c>
-      <c r="Q17" s="22">
-        <f>P17*N17</f>
         <v>1.7129999999999999</v>
       </c>
-      <c r="R17" s="21"/>
-      <c r="S17" s="21"/>
-    </row>
-    <row r="18" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="R17" s="20"/>
+    </row>
+    <row r="18" spans="1:18" ht="24" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="16">
         <f>ROW(B18) - ROW($B$7)</f>
         <v>11</v>
       </c>
-      <c r="C18" s="23" t="s">
+      <c r="C18" s="22" t="s">
         <v>6</v>
       </c>
       <c r="D18" s="14" t="s">
@@ -2963,8 +2835,8 @@
       <c r="H18" s="14" t="s">
         <v>266</v>
       </c>
-      <c r="I18" s="21" t="s">
-        <v>397</v>
+      <c r="I18" s="20" t="s">
+        <v>396</v>
       </c>
       <c r="J18" s="14" t="s">
         <v>304</v>
@@ -2976,88 +2848,86 @@
         <v>2</v>
       </c>
       <c r="M18" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="N18" s="14">
         <v>50</v>
       </c>
-      <c r="O18" s="51" t="s">
-        <v>403</v>
+      <c r="O18" s="43" t="s">
+        <v>402</v>
       </c>
       <c r="P18" s="15">
         <v>9.1999999999999998E-3</v>
       </c>
       <c r="Q18" s="15">
-        <f>P18*N18</f>
+        <f t="shared" si="0"/>
         <v>0.45999999999999996</v>
       </c>
       <c r="R18" s="14"/>
-      <c r="S18" s="20"/>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="17">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="C19" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="E19" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="F19" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="G19" s="20" t="s">
+        <v>222</v>
+      </c>
+      <c r="H19" s="20" t="s">
+        <v>266</v>
+      </c>
+      <c r="I19" s="20" t="s">
+        <v>396</v>
+      </c>
+      <c r="J19" s="20" t="s">
+        <v>305</v>
+      </c>
+      <c r="K19" s="20" t="s">
+        <v>362</v>
+      </c>
+      <c r="L19" s="20">
+        <v>1</v>
+      </c>
+      <c r="M19" s="14">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="N19" s="20">
+        <v>100</v>
+      </c>
+      <c r="O19" s="43" t="s">
+        <v>402</v>
+      </c>
+      <c r="P19" s="21">
+        <v>2.8E-3</v>
+      </c>
+      <c r="Q19" s="21">
         <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="C19" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="D19" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="E19" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="F19" s="21" t="s">
-        <v>170</v>
-      </c>
-      <c r="G19" s="21" t="s">
-        <v>222</v>
-      </c>
-      <c r="H19" s="21" t="s">
-        <v>266</v>
-      </c>
-      <c r="I19" s="21" t="s">
-        <v>397</v>
-      </c>
-      <c r="J19" s="21" t="s">
-        <v>305</v>
-      </c>
-      <c r="K19" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="L19" s="21">
-        <v>1</v>
-      </c>
-      <c r="M19" s="14">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="N19" s="21">
-        <v>100</v>
-      </c>
-      <c r="O19" s="51" t="s">
-        <v>403</v>
-      </c>
-      <c r="P19" s="22">
-        <v>2.8E-3</v>
-      </c>
-      <c r="Q19" s="22">
-        <f>P19*N19</f>
         <v>0.27999999999999997</v>
       </c>
-      <c r="R19" s="21"/>
-      <c r="S19" s="21"/>
-    </row>
-    <row r="20" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="R19" s="20"/>
+    </row>
+    <row r="20" spans="1:18" ht="24" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="16">
         <f>ROW(B20) - ROW($B$7)</f>
         <v>13</v>
       </c>
-      <c r="C20" s="23" t="s">
+      <c r="C20" s="22" t="s">
         <v>6</v>
       </c>
       <c r="D20" s="14" t="s">
@@ -3075,8 +2945,8 @@
       <c r="H20" s="14" t="s">
         <v>266</v>
       </c>
-      <c r="I20" s="21" t="s">
-        <v>397</v>
+      <c r="I20" s="20" t="s">
+        <v>396</v>
       </c>
       <c r="J20" s="14" t="s">
         <v>306</v>
@@ -3088,88 +2958,86 @@
         <v>4</v>
       </c>
       <c r="M20" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>40</v>
       </c>
       <c r="N20" s="14">
         <v>50</v>
       </c>
-      <c r="O20" s="51" t="s">
-        <v>403</v>
+      <c r="O20" s="43" t="s">
+        <v>402</v>
       </c>
       <c r="P20" s="15">
         <v>7.7999999999999996E-3</v>
       </c>
       <c r="Q20" s="15">
-        <f>P20*N20</f>
+        <f t="shared" si="0"/>
         <v>0.38999999999999996</v>
       </c>
       <c r="R20" s="14"/>
-      <c r="S20" s="20"/>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="17">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="C21" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="D21" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="F21" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="G21" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="H21" s="20" t="s">
+        <v>269</v>
+      </c>
+      <c r="I21" s="20" t="s">
+        <v>396</v>
+      </c>
+      <c r="J21" s="20" t="s">
+        <v>307</v>
+      </c>
+      <c r="K21" s="20" t="s">
+        <v>364</v>
+      </c>
+      <c r="L21" s="20">
+        <v>4</v>
+      </c>
+      <c r="M21" s="14">
+        <f t="shared" si="2"/>
+        <v>40</v>
+      </c>
+      <c r="N21" s="20">
+        <v>100</v>
+      </c>
+      <c r="O21" s="43" t="s">
+        <v>402</v>
+      </c>
+      <c r="P21" s="21">
+        <v>3.8E-3</v>
+      </c>
+      <c r="Q21" s="21">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="C21" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="D21" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="E21" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="F21" s="21" t="s">
-        <v>170</v>
-      </c>
-      <c r="G21" s="21" t="s">
-        <v>224</v>
-      </c>
-      <c r="H21" s="21" t="s">
-        <v>269</v>
-      </c>
-      <c r="I21" s="21" t="s">
-        <v>397</v>
-      </c>
-      <c r="J21" s="21" t="s">
-        <v>307</v>
-      </c>
-      <c r="K21" s="21" t="s">
-        <v>364</v>
-      </c>
-      <c r="L21" s="21">
-        <v>4</v>
-      </c>
-      <c r="M21" s="14">
-        <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-      <c r="N21" s="21">
-        <v>100</v>
-      </c>
-      <c r="O21" s="51" t="s">
-        <v>403</v>
-      </c>
-      <c r="P21" s="22">
-        <v>3.8E-3</v>
-      </c>
-      <c r="Q21" s="22">
-        <f>P21*N21</f>
         <v>0.38</v>
       </c>
-      <c r="R21" s="21"/>
-      <c r="S21" s="21"/>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R21" s="20"/>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="16">
         <f>ROW(B22) - ROW($B$7)</f>
         <v>15</v>
       </c>
-      <c r="C22" s="23" t="s">
+      <c r="C22" s="22" t="s">
         <v>6</v>
       </c>
       <c r="D22" s="14" t="s">
@@ -3187,8 +3055,8 @@
       <c r="H22" s="14" t="s">
         <v>266</v>
       </c>
-      <c r="I22" s="21" t="s">
-        <v>397</v>
+      <c r="I22" s="20" t="s">
+        <v>396</v>
       </c>
       <c r="J22" s="14" t="s">
         <v>308</v>
@@ -3200,88 +3068,86 @@
         <v>2</v>
       </c>
       <c r="M22" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="N22" s="14">
         <v>40</v>
       </c>
-      <c r="O22" s="51" t="s">
-        <v>403</v>
+      <c r="O22" s="43" t="s">
+        <v>402</v>
       </c>
       <c r="P22" s="15">
         <v>2.0899999999999998E-2</v>
       </c>
       <c r="Q22" s="15">
-        <f>P22*N22</f>
+        <f t="shared" si="0"/>
         <v>0.83599999999999997</v>
       </c>
       <c r="R22" s="14"/>
-      <c r="S22" s="20"/>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="17">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="C23" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="D23" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="E23" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="F23" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="G23" s="20" t="s">
+        <v>226</v>
+      </c>
+      <c r="H23" s="20" t="s">
+        <v>266</v>
+      </c>
+      <c r="I23" s="20" t="s">
+        <v>396</v>
+      </c>
+      <c r="J23" s="20" t="s">
+        <v>309</v>
+      </c>
+      <c r="K23" s="20" t="s">
+        <v>366</v>
+      </c>
+      <c r="L23" s="20">
+        <v>1</v>
+      </c>
+      <c r="M23" s="14">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="N23" s="20">
+        <v>50</v>
+      </c>
+      <c r="O23" s="43" t="s">
+        <v>402</v>
+      </c>
+      <c r="P23" s="21">
+        <v>9.4000000000000004E-3</v>
+      </c>
+      <c r="Q23" s="21">
         <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="C23" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="D23" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="E23" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="F23" s="21" t="s">
-        <v>170</v>
-      </c>
-      <c r="G23" s="21" t="s">
-        <v>226</v>
-      </c>
-      <c r="H23" s="21" t="s">
-        <v>266</v>
-      </c>
-      <c r="I23" s="21" t="s">
-        <v>397</v>
-      </c>
-      <c r="J23" s="21" t="s">
-        <v>309</v>
-      </c>
-      <c r="K23" s="21" t="s">
-        <v>366</v>
-      </c>
-      <c r="L23" s="21">
-        <v>1</v>
-      </c>
-      <c r="M23" s="14">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="N23" s="21">
-        <v>50</v>
-      </c>
-      <c r="O23" s="51" t="s">
-        <v>403</v>
-      </c>
-      <c r="P23" s="22">
-        <v>9.4000000000000004E-3</v>
-      </c>
-      <c r="Q23" s="22">
-        <f>P23*N23</f>
         <v>0.47000000000000003</v>
       </c>
-      <c r="R23" s="21"/>
-      <c r="S23" s="21"/>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R23" s="20"/>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="16">
         <f>ROW(B24) - ROW($B$7)</f>
         <v>17</v>
       </c>
-      <c r="C24" s="24" t="s">
+      <c r="C24" s="23" t="s">
         <v>6</v>
       </c>
       <c r="D24" s="14" t="s">
@@ -3300,100 +3166,98 @@
         <v>271</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="J24" s="14" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="K24" s="14" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="L24" s="14">
         <v>1</v>
       </c>
       <c r="M24" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="N24" s="14">
         <v>20</v>
       </c>
-      <c r="O24" s="51" t="s">
-        <v>403</v>
+      <c r="O24" s="43" t="s">
+        <v>402</v>
       </c>
       <c r="P24" s="15">
         <v>4.41E-2</v>
       </c>
       <c r="Q24" s="15">
-        <f>P24*N24</f>
+        <f t="shared" si="0"/>
         <v>0.88200000000000001</v>
       </c>
       <c r="R24" s="14"/>
-      <c r="S24" s="20"/>
-    </row>
-    <row r="25" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:18" ht="36" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="17">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="C25" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="E25" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="F25" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="G25" s="20" t="s">
+        <v>228</v>
+      </c>
+      <c r="H25" s="20" t="s">
+        <v>271</v>
+      </c>
+      <c r="I25" s="20" t="s">
+        <v>396</v>
+      </c>
+      <c r="J25" s="20" t="s">
+        <v>310</v>
+      </c>
+      <c r="K25" s="14" t="s">
+        <v>396</v>
+      </c>
+      <c r="L25" s="20">
+        <v>1</v>
+      </c>
+      <c r="M25" s="14">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="N25" s="20">
+        <v>20</v>
+      </c>
+      <c r="O25" s="43" t="s">
+        <v>402</v>
+      </c>
+      <c r="P25" s="21">
+        <v>3.4799999999999998E-2</v>
+      </c>
+      <c r="Q25" s="21">
         <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="C25" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D25" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="E25" s="21" t="s">
-        <v>118</v>
-      </c>
-      <c r="F25" s="21" t="s">
-        <v>177</v>
-      </c>
-      <c r="G25" s="21" t="s">
-        <v>228</v>
-      </c>
-      <c r="H25" s="21" t="s">
-        <v>271</v>
-      </c>
-      <c r="I25" s="21" t="s">
-        <v>397</v>
-      </c>
-      <c r="J25" s="21" t="s">
-        <v>310</v>
-      </c>
-      <c r="K25" s="14" t="s">
-        <v>397</v>
-      </c>
-      <c r="L25" s="21">
-        <v>1</v>
-      </c>
-      <c r="M25" s="14">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="N25" s="21">
-        <v>20</v>
-      </c>
-      <c r="O25" s="51" t="s">
-        <v>403</v>
-      </c>
-      <c r="P25" s="22">
-        <v>3.4799999999999998E-2</v>
-      </c>
-      <c r="Q25" s="22">
-        <f>P25*N25</f>
         <v>0.69599999999999995</v>
       </c>
-      <c r="R25" s="21"/>
-      <c r="S25" s="21"/>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R25" s="20"/>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="16">
         <f>ROW(B26) - ROW($B$7)</f>
         <v>19</v>
       </c>
-      <c r="C26" s="23" t="s">
+      <c r="C26" s="22" t="s">
         <v>9</v>
       </c>
       <c r="D26" s="14" t="s">
@@ -3412,100 +3276,98 @@
         <v>272</v>
       </c>
       <c r="I26" s="14" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="J26" s="14" t="s">
         <v>311</v>
       </c>
       <c r="K26" s="14" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="L26" s="14">
         <v>1</v>
       </c>
       <c r="M26" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="N26" s="14">
         <v>15</v>
       </c>
-      <c r="O26" s="51" t="s">
-        <v>403</v>
+      <c r="O26" s="43" t="s">
+        <v>402</v>
       </c>
       <c r="P26" s="15">
         <v>0.11</v>
       </c>
       <c r="Q26" s="15">
-        <f>P26*N26</f>
+        <f t="shared" si="0"/>
         <v>1.65</v>
       </c>
       <c r="R26" s="14"/>
-      <c r="S26" s="20"/>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="C27" s="23" t="s">
+      <c r="C27" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="D27" s="21" t="s">
+      <c r="D27" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="E27" s="21" t="s">
+      <c r="E27" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="F27" s="21" t="s">
+      <c r="F27" s="20" t="s">
         <v>177</v>
       </c>
-      <c r="G27" s="21" t="s">
+      <c r="G27" s="20" t="s">
         <v>230</v>
       </c>
-      <c r="H27" s="21" t="s">
+      <c r="H27" s="20" t="s">
         <v>273</v>
       </c>
-      <c r="I27" s="21" t="s">
-        <v>397</v>
+      <c r="I27" s="20" t="s">
+        <v>396</v>
       </c>
       <c r="J27" s="14" t="s">
         <v>10</v>
       </c>
       <c r="K27" s="14" t="s">
-        <v>397</v>
-      </c>
-      <c r="L27" s="21">
+        <v>396</v>
+      </c>
+      <c r="L27" s="20">
         <v>1</v>
       </c>
       <c r="M27" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="N27" s="21">
+      <c r="N27" s="20">
         <v>20</v>
       </c>
-      <c r="O27" s="51" t="s">
-        <v>403</v>
-      </c>
-      <c r="P27" s="22">
+      <c r="O27" s="43" t="s">
+        <v>402</v>
+      </c>
+      <c r="P27" s="21">
         <v>3.44E-2</v>
       </c>
-      <c r="Q27" s="22">
-        <f>P27*N27</f>
+      <c r="Q27" s="21">
+        <f t="shared" si="0"/>
         <v>0.68799999999999994</v>
       </c>
-      <c r="R27" s="21"/>
-      <c r="S27" s="21"/>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R27" s="20"/>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="16">
         <f>ROW(B28) - ROW($B$7)</f>
         <v>21</v>
       </c>
-      <c r="C28" s="23" t="s">
+      <c r="C28" s="22" t="s">
         <v>9</v>
       </c>
       <c r="D28" s="14" t="s">
@@ -3524,100 +3386,98 @@
         <v>272</v>
       </c>
       <c r="I28" s="14" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="J28" s="14" t="s">
         <v>312</v>
       </c>
       <c r="K28" s="14" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="L28" s="14">
         <v>2</v>
       </c>
       <c r="M28" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="N28" s="14">
         <v>50</v>
       </c>
-      <c r="O28" s="51" t="s">
-        <v>403</v>
+      <c r="O28" s="43" t="s">
+        <v>402</v>
       </c>
       <c r="P28" s="15">
         <v>1.4500000000000001E-2</v>
       </c>
       <c r="Q28" s="15">
-        <f>P28*N28</f>
+        <f t="shared" si="0"/>
         <v>0.72500000000000009</v>
       </c>
       <c r="R28" s="14"/>
-      <c r="S28" s="20"/>
-    </row>
-    <row r="29" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:18" ht="24" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="17">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="C29" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="E29" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="F29" s="20" t="s">
+        <v>403</v>
+      </c>
+      <c r="G29" s="20" t="s">
+        <v>406</v>
+      </c>
+      <c r="H29" s="20" t="s">
+        <v>274</v>
+      </c>
+      <c r="I29" s="20" t="s">
+        <v>396</v>
+      </c>
+      <c r="J29" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="K29" s="14" t="s">
+        <v>396</v>
+      </c>
+      <c r="L29" s="20">
+        <v>1</v>
+      </c>
+      <c r="M29" s="14">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="N29" s="20">
+        <v>12</v>
+      </c>
+      <c r="O29" s="43" t="s">
+        <v>402</v>
+      </c>
+      <c r="P29" s="21">
+        <v>6.4500000000000002E-2</v>
+      </c>
+      <c r="Q29" s="21">
         <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="C29" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="D29" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="E29" s="21" t="s">
-        <v>122</v>
-      </c>
-      <c r="F29" s="21" t="s">
-        <v>404</v>
-      </c>
-      <c r="G29" s="21" t="s">
-        <v>407</v>
-      </c>
-      <c r="H29" s="21" t="s">
-        <v>274</v>
-      </c>
-      <c r="I29" s="21" t="s">
-        <v>397</v>
-      </c>
-      <c r="J29" s="21" t="s">
-        <v>232</v>
-      </c>
-      <c r="K29" s="14" t="s">
-        <v>397</v>
-      </c>
-      <c r="L29" s="21">
-        <v>1</v>
-      </c>
-      <c r="M29" s="14">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="N29" s="21">
-        <v>12</v>
-      </c>
-      <c r="O29" s="51" t="s">
-        <v>403</v>
-      </c>
-      <c r="P29" s="22">
-        <v>6.4500000000000002E-2</v>
-      </c>
-      <c r="Q29" s="22">
-        <f>P29*N29</f>
         <v>0.77400000000000002</v>
       </c>
-      <c r="R29" s="21"/>
-      <c r="S29" s="21"/>
-    </row>
-    <row r="30" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+      <c r="R29" s="20"/>
+    </row>
+    <row r="30" spans="1:18" ht="48" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="16">
         <f>ROW(B30) - ROW($B$7)</f>
         <v>23</v>
       </c>
-      <c r="C30" s="23" t="s">
+      <c r="C30" s="22" t="s">
         <v>12</v>
       </c>
       <c r="D30" s="14" t="s">
@@ -3627,7 +3487,7 @@
         <v>123</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="G30" s="14" t="s">
         <v>180</v>
@@ -3635,101 +3495,99 @@
       <c r="H30" s="14" t="s">
         <v>275</v>
       </c>
-      <c r="I30" s="21" t="s">
-        <v>397</v>
+      <c r="I30" s="20" t="s">
+        <v>396</v>
       </c>
       <c r="J30" s="14" t="s">
         <v>313</v>
       </c>
       <c r="K30" s="14" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="L30" s="14">
         <v>1</v>
       </c>
       <c r="M30" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="N30" s="14">
         <v>15</v>
       </c>
-      <c r="O30" s="51" t="s">
-        <v>403</v>
+      <c r="O30" s="43" t="s">
+        <v>402</v>
       </c>
       <c r="P30" s="15">
         <v>0.24970000000000001</v>
       </c>
       <c r="Q30" s="15">
-        <f>P30*N30</f>
+        <f t="shared" si="0"/>
         <v>3.7455000000000003</v>
       </c>
       <c r="R30" s="14"/>
-      <c r="S30" s="20"/>
-    </row>
-    <row r="31" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:18" ht="48" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="B31" s="17">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="C31" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="D31" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="E31" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="F31" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="G31" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="H31" s="20" t="s">
+        <v>276</v>
+      </c>
+      <c r="I31" s="20" t="s">
+        <v>396</v>
+      </c>
+      <c r="J31" s="20" t="s">
+        <v>314</v>
+      </c>
+      <c r="K31" s="14" t="s">
+        <v>396</v>
+      </c>
+      <c r="L31" s="20">
+        <v>2</v>
+      </c>
+      <c r="M31" s="14">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="N31" s="20">
+        <v>30</v>
+      </c>
+      <c r="O31" s="43" t="s">
+        <v>402</v>
+      </c>
+      <c r="P31" s="21">
+        <v>5.0500000000000003E-2</v>
+      </c>
+      <c r="Q31" s="21">
         <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="C31" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="D31" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="E31" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="F31" s="21" t="s">
-        <v>181</v>
-      </c>
-      <c r="G31" s="21" t="s">
-        <v>233</v>
-      </c>
-      <c r="H31" s="21" t="s">
-        <v>276</v>
-      </c>
-      <c r="I31" s="21" t="s">
-        <v>397</v>
-      </c>
-      <c r="J31" s="21" t="s">
-        <v>314</v>
-      </c>
-      <c r="K31" s="14" t="s">
-        <v>397</v>
-      </c>
-      <c r="L31" s="21">
-        <v>2</v>
-      </c>
-      <c r="M31" s="14">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="N31" s="21">
-        <v>30</v>
-      </c>
-      <c r="O31" s="51" t="s">
-        <v>403</v>
-      </c>
-      <c r="P31" s="22">
-        <v>5.0500000000000003E-2</v>
-      </c>
-      <c r="Q31" s="22">
-        <f>P31*N31</f>
         <v>1.5150000000000001</v>
       </c>
-      <c r="R31" s="21"/>
-      <c r="S31" s="21"/>
-    </row>
-    <row r="32" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+      <c r="R31" s="20"/>
+    </row>
+    <row r="32" spans="1:18" ht="48" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="16">
         <f>ROW(B32) - ROW($B$7)</f>
         <v>25</v>
       </c>
-      <c r="C32" s="23" t="s">
+      <c r="C32" s="22" t="s">
         <v>14</v>
       </c>
       <c r="D32" s="14" t="s">
@@ -3747,101 +3605,99 @@
       <c r="H32" s="14" t="s">
         <v>277</v>
       </c>
-      <c r="I32" s="21" t="s">
-        <v>397</v>
+      <c r="I32" s="20" t="s">
+        <v>396</v>
       </c>
       <c r="J32" s="14" t="s">
         <v>315</v>
       </c>
       <c r="K32" s="14" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="L32" s="14">
         <v>1</v>
       </c>
       <c r="M32" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="N32" s="14">
         <v>20</v>
       </c>
-      <c r="O32" s="51" t="s">
-        <v>403</v>
+      <c r="O32" s="43" t="s">
+        <v>402</v>
       </c>
       <c r="P32" s="15">
         <v>3.5700000000000003E-2</v>
       </c>
       <c r="Q32" s="15">
-        <f>P32*N32</f>
+        <f t="shared" si="0"/>
         <v>0.71400000000000008</v>
       </c>
       <c r="R32" s="14"/>
-      <c r="S32" s="20"/>
-    </row>
-    <row r="33" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:18" ht="48" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="B33" s="17">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="C33" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="D33" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="E33" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="F33" s="20" t="s">
+        <v>403</v>
+      </c>
+      <c r="G33" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="H33" s="20" t="s">
+        <v>278</v>
+      </c>
+      <c r="I33" s="20" t="s">
+        <v>396</v>
+      </c>
+      <c r="J33" s="20" t="s">
+        <v>316</v>
+      </c>
+      <c r="K33" s="14" t="s">
+        <v>396</v>
+      </c>
+      <c r="L33" s="20">
+        <v>1</v>
+      </c>
+      <c r="M33" s="14">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="N33" s="20">
+        <v>15</v>
+      </c>
+      <c r="O33" s="43" t="s">
+        <v>402</v>
+      </c>
+      <c r="P33" s="21">
+        <v>0.15010000000000001</v>
+      </c>
+      <c r="Q33" s="21">
         <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="C33" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="D33" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="E33" s="21" t="s">
-        <v>126</v>
-      </c>
-      <c r="F33" s="21" t="s">
-        <v>404</v>
-      </c>
-      <c r="G33" s="21" t="s">
-        <v>183</v>
-      </c>
-      <c r="H33" s="21" t="s">
-        <v>278</v>
-      </c>
-      <c r="I33" s="21" t="s">
-        <v>397</v>
-      </c>
-      <c r="J33" s="21" t="s">
-        <v>316</v>
-      </c>
-      <c r="K33" s="14" t="s">
-        <v>397</v>
-      </c>
-      <c r="L33" s="21">
-        <v>1</v>
-      </c>
-      <c r="M33" s="14">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="N33" s="21">
-        <v>15</v>
-      </c>
-      <c r="O33" s="51" t="s">
-        <v>403</v>
-      </c>
-      <c r="P33" s="22">
-        <v>0.15010000000000001</v>
-      </c>
-      <c r="Q33" s="22">
-        <f>P33*N33</f>
         <v>2.2515000000000001</v>
       </c>
-      <c r="R33" s="21"/>
-      <c r="S33" s="21"/>
-    </row>
-    <row r="34" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+      <c r="R33" s="20"/>
+    </row>
+    <row r="34" spans="1:18" ht="48" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="B34" s="16">
         <f>ROW(B34) - ROW($B$7)</f>
         <v>27</v>
       </c>
-      <c r="C34" s="23" t="s">
+      <c r="C34" s="22" t="s">
         <v>12</v>
       </c>
       <c r="D34" s="14" t="s">
@@ -3850,8 +3706,8 @@
       <c r="E34" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="F34" s="21" t="s">
-        <v>404</v>
+      <c r="F34" s="20" t="s">
+        <v>403</v>
       </c>
       <c r="G34" s="14" t="s">
         <v>184</v>
@@ -3859,101 +3715,99 @@
       <c r="H34" s="14" t="s">
         <v>279</v>
       </c>
-      <c r="I34" s="21" t="s">
-        <v>397</v>
+      <c r="I34" s="20" t="s">
+        <v>396</v>
       </c>
       <c r="J34" s="14" t="s">
         <v>317</v>
       </c>
       <c r="K34" s="14" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="L34" s="14">
         <v>1</v>
       </c>
       <c r="M34" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="N34" s="14">
         <v>15</v>
       </c>
-      <c r="O34" s="51" t="s">
-        <v>403</v>
+      <c r="O34" s="43" t="s">
+        <v>402</v>
       </c>
       <c r="P34" s="15">
         <v>0.15890000000000001</v>
       </c>
       <c r="Q34" s="15">
-        <f>P34*N34</f>
+        <f t="shared" si="0"/>
         <v>2.3835000000000002</v>
       </c>
       <c r="R34" s="14"/>
-      <c r="S34" s="20"/>
-    </row>
-    <row r="35" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:18" ht="24" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="B35" s="17">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="C35" s="23" t="s">
+        <v>397</v>
+      </c>
+      <c r="D35" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="E35" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="F35" s="20" t="s">
+        <v>403</v>
+      </c>
+      <c r="G35" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="H35" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="I35" s="20" t="s">
+        <v>396</v>
+      </c>
+      <c r="J35" s="20" t="s">
+        <v>318</v>
+      </c>
+      <c r="K35" s="14" t="s">
+        <v>396</v>
+      </c>
+      <c r="L35" s="20">
+        <v>1</v>
+      </c>
+      <c r="M35" s="14">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="N35" s="20">
+        <v>11</v>
+      </c>
+      <c r="O35" s="43" t="s">
+        <v>402</v>
+      </c>
+      <c r="P35" s="21">
+        <v>0.36820000000000003</v>
+      </c>
+      <c r="Q35" s="21">
         <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
-      <c r="C35" s="24" t="s">
-        <v>398</v>
-      </c>
-      <c r="D35" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="E35" s="21" t="s">
-        <v>128</v>
-      </c>
-      <c r="F35" s="21" t="s">
-        <v>404</v>
-      </c>
-      <c r="G35" s="21" t="s">
-        <v>185</v>
-      </c>
-      <c r="H35" s="21" t="s">
-        <v>280</v>
-      </c>
-      <c r="I35" s="21" t="s">
-        <v>397</v>
-      </c>
-      <c r="J35" s="21" t="s">
-        <v>318</v>
-      </c>
-      <c r="K35" s="14" t="s">
-        <v>397</v>
-      </c>
-      <c r="L35" s="21">
-        <v>1</v>
-      </c>
-      <c r="M35" s="14">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="N35" s="21">
-        <v>11</v>
-      </c>
-      <c r="O35" s="51" t="s">
-        <v>403</v>
-      </c>
-      <c r="P35" s="22">
-        <v>0.36820000000000003</v>
-      </c>
-      <c r="Q35" s="22">
-        <f>P35*N35</f>
         <v>4.0502000000000002</v>
       </c>
-      <c r="R35" s="21"/>
-      <c r="S35" s="21"/>
-    </row>
-    <row r="36" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+      <c r="R35" s="20"/>
+    </row>
+    <row r="36" spans="1:18" ht="48" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="B36" s="16">
         <f>ROW(B36) - ROW($B$7)</f>
         <v>29</v>
       </c>
-      <c r="C36" s="23" t="s">
+      <c r="C36" s="22" t="s">
         <v>12</v>
       </c>
       <c r="D36" s="14" t="s">
@@ -3962,8 +3816,8 @@
       <c r="E36" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="F36" s="21" t="s">
-        <v>404</v>
+      <c r="F36" s="20" t="s">
+        <v>403</v>
       </c>
       <c r="G36" s="14" t="s">
         <v>186</v>
@@ -3971,101 +3825,99 @@
       <c r="H36" s="14" t="s">
         <v>279</v>
       </c>
-      <c r="I36" s="21" t="s">
-        <v>397</v>
+      <c r="I36" s="20" t="s">
+        <v>396</v>
       </c>
       <c r="J36" s="14" t="s">
         <v>319</v>
       </c>
       <c r="K36" s="14" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="L36" s="14">
         <v>1</v>
       </c>
       <c r="M36" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="N36" s="14">
         <v>15</v>
       </c>
-      <c r="O36" s="51" t="s">
-        <v>403</v>
+      <c r="O36" s="43" t="s">
+        <v>402</v>
       </c>
       <c r="P36" s="15">
         <v>0.15840000000000001</v>
       </c>
       <c r="Q36" s="15">
-        <f>P36*N36</f>
+        <f t="shared" si="0"/>
         <v>2.3760000000000003</v>
       </c>
       <c r="R36" s="14"/>
-      <c r="S36" s="20"/>
-    </row>
-    <row r="37" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:18" ht="48" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="B37" s="17">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="C37" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="D37" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E37" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="F37" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="G37" s="20" t="s">
+        <v>235</v>
+      </c>
+      <c r="H37" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="I37" s="20" t="s">
+        <v>396</v>
+      </c>
+      <c r="J37" s="20" t="s">
+        <v>320</v>
+      </c>
+      <c r="K37" s="14" t="s">
+        <v>396</v>
+      </c>
+      <c r="L37" s="20">
+        <v>1</v>
+      </c>
+      <c r="M37" s="14">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="N37" s="20">
+        <v>20</v>
+      </c>
+      <c r="O37" s="43" t="s">
+        <v>402</v>
+      </c>
+      <c r="P37" s="21">
+        <v>1.8800000000000001E-2</v>
+      </c>
+      <c r="Q37" s="21">
         <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="C37" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="D37" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="E37" s="21" t="s">
-        <v>130</v>
-      </c>
-      <c r="F37" s="21" t="s">
-        <v>187</v>
-      </c>
-      <c r="G37" s="21" t="s">
-        <v>235</v>
-      </c>
-      <c r="H37" s="21" t="s">
-        <v>277</v>
-      </c>
-      <c r="I37" s="21" t="s">
-        <v>397</v>
-      </c>
-      <c r="J37" s="21" t="s">
-        <v>320</v>
-      </c>
-      <c r="K37" s="14" t="s">
-        <v>397</v>
-      </c>
-      <c r="L37" s="21">
-        <v>1</v>
-      </c>
-      <c r="M37" s="14">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="N37" s="21">
-        <v>20</v>
-      </c>
-      <c r="O37" s="51" t="s">
-        <v>403</v>
-      </c>
-      <c r="P37" s="22">
-        <v>1.8800000000000001E-2</v>
-      </c>
-      <c r="Q37" s="22">
-        <f>P37*N37</f>
         <v>0.376</v>
       </c>
-      <c r="R37" s="21"/>
-      <c r="S37" s="21"/>
-    </row>
-    <row r="38" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="R37" s="20"/>
+    </row>
+    <row r="38" spans="1:18" ht="24" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="B38" s="16">
         <f>ROW(B38) - ROW($B$7)</f>
         <v>31</v>
       </c>
-      <c r="C38" s="23" t="s">
+      <c r="C38" s="22" t="s">
         <v>15</v>
       </c>
       <c r="D38" s="14" t="s">
@@ -4075,7 +3927,7 @@
         <v>131</v>
       </c>
       <c r="F38" s="14" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="G38" s="14" t="s">
         <v>188</v>
@@ -4083,101 +3935,99 @@
       <c r="H38" s="14" t="s">
         <v>281</v>
       </c>
-      <c r="I38" s="21" t="s">
-        <v>397</v>
+      <c r="I38" s="20" t="s">
+        <v>396</v>
       </c>
       <c r="J38" s="14" t="s">
         <v>321</v>
       </c>
       <c r="K38" s="14" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="L38" s="14">
         <v>1</v>
       </c>
       <c r="M38" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="N38" s="14">
         <v>11</v>
       </c>
-      <c r="O38" s="51" t="s">
-        <v>403</v>
+      <c r="O38" s="43" t="s">
+        <v>402</v>
       </c>
       <c r="P38" s="15">
         <v>0.67759999999999998</v>
       </c>
       <c r="Q38" s="15">
-        <f>P38*N38</f>
+        <f t="shared" si="0"/>
         <v>7.4535999999999998</v>
       </c>
       <c r="R38" s="14"/>
-      <c r="S38" s="20"/>
-    </row>
-    <row r="39" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:18" ht="24" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="B39" s="17">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="C39" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D39" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="E39" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="F39" s="14" t="s">
+        <v>403</v>
+      </c>
+      <c r="G39" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="H39" s="20" t="s">
+        <v>282</v>
+      </c>
+      <c r="I39" s="20" t="s">
+        <v>396</v>
+      </c>
+      <c r="J39" s="20" t="s">
+        <v>322</v>
+      </c>
+      <c r="K39" s="20" t="s">
+        <v>367</v>
+      </c>
+      <c r="L39" s="20">
+        <v>1</v>
+      </c>
+      <c r="M39" s="14">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="N39" s="20">
+        <v>15</v>
+      </c>
+      <c r="O39" s="43" t="s">
+        <v>402</v>
+      </c>
+      <c r="P39" s="21">
+        <v>0.16950000000000001</v>
+      </c>
+      <c r="Q39" s="21">
         <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
-      <c r="C39" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="D39" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="E39" s="21" t="s">
-        <v>132</v>
-      </c>
-      <c r="F39" s="14" t="s">
-        <v>404</v>
-      </c>
-      <c r="G39" s="21" t="s">
-        <v>189</v>
-      </c>
-      <c r="H39" s="21" t="s">
-        <v>282</v>
-      </c>
-      <c r="I39" s="21" t="s">
-        <v>397</v>
-      </c>
-      <c r="J39" s="21" t="s">
-        <v>322</v>
-      </c>
-      <c r="K39" s="21" t="s">
-        <v>367</v>
-      </c>
-      <c r="L39" s="21">
-        <v>1</v>
-      </c>
-      <c r="M39" s="14">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="N39" s="21">
-        <v>15</v>
-      </c>
-      <c r="O39" s="51" t="s">
-        <v>403</v>
-      </c>
-      <c r="P39" s="22">
-        <v>0.16950000000000001</v>
-      </c>
-      <c r="Q39" s="22">
-        <f>P39*N39</f>
         <v>2.5425</v>
       </c>
-      <c r="R39" s="21"/>
-      <c r="S39" s="21"/>
-    </row>
-    <row r="40" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+      <c r="R39" s="20"/>
+    </row>
+    <row r="40" spans="1:18" ht="36" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
       <c r="B40" s="16">
         <f>ROW(B40) - ROW($B$7)</f>
         <v>33</v>
       </c>
-      <c r="C40" s="23" t="s">
+      <c r="C40" s="22" t="s">
         <v>17</v>
       </c>
       <c r="D40" s="14" t="s">
@@ -4195,101 +4045,99 @@
       <c r="H40" s="14" t="s">
         <v>283</v>
       </c>
-      <c r="I40" s="21" t="s">
-        <v>397</v>
+      <c r="I40" s="20" t="s">
+        <v>396</v>
       </c>
       <c r="J40" s="14" t="s">
         <v>323</v>
       </c>
       <c r="K40" s="14" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="L40" s="14">
         <v>2</v>
       </c>
       <c r="M40" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="N40" s="14">
         <v>40</v>
       </c>
-      <c r="O40" s="51" t="s">
-        <v>403</v>
+      <c r="O40" s="43" t="s">
+        <v>402</v>
       </c>
       <c r="P40" s="15">
         <v>3.0800000000000001E-2</v>
       </c>
       <c r="Q40" s="15">
-        <f>P40*N40</f>
+        <f t="shared" si="0"/>
         <v>1.232</v>
       </c>
       <c r="R40" s="14"/>
-      <c r="S40" s="20"/>
-    </row>
-    <row r="41" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="1:18" ht="36" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="B41" s="17">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="C41" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="D41" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="E41" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="F41" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="G41" s="20" t="s">
+        <v>237</v>
+      </c>
+      <c r="H41" s="20" t="s">
+        <v>283</v>
+      </c>
+      <c r="I41" s="20" t="s">
+        <v>396</v>
+      </c>
+      <c r="J41" s="20" t="s">
+        <v>324</v>
+      </c>
+      <c r="K41" s="14" t="s">
+        <v>396</v>
+      </c>
+      <c r="L41" s="20">
+        <v>2</v>
+      </c>
+      <c r="M41" s="14">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="N41" s="20">
+        <v>40</v>
+      </c>
+      <c r="O41" s="43" t="s">
+        <v>402</v>
+      </c>
+      <c r="P41" s="21">
+        <v>3.3599999999999998E-2</v>
+      </c>
+      <c r="Q41" s="21">
         <f t="shared" si="0"/>
-        <v>34</v>
-      </c>
-      <c r="C41" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="D41" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="E41" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="F41" s="21" t="s">
-        <v>191</v>
-      </c>
-      <c r="G41" s="21" t="s">
-        <v>237</v>
-      </c>
-      <c r="H41" s="21" t="s">
-        <v>283</v>
-      </c>
-      <c r="I41" s="21" t="s">
-        <v>397</v>
-      </c>
-      <c r="J41" s="21" t="s">
-        <v>324</v>
-      </c>
-      <c r="K41" s="14" t="s">
-        <v>397</v>
-      </c>
-      <c r="L41" s="21">
-        <v>2</v>
-      </c>
-      <c r="M41" s="14">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="N41" s="21">
-        <v>40</v>
-      </c>
-      <c r="O41" s="51" t="s">
-        <v>403</v>
-      </c>
-      <c r="P41" s="22">
-        <v>3.3599999999999998E-2</v>
-      </c>
-      <c r="Q41" s="22">
-        <f>P41*N41</f>
         <v>1.3439999999999999</v>
       </c>
-      <c r="R41" s="21"/>
-      <c r="S41" s="21"/>
-    </row>
-    <row r="42" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+      <c r="R41" s="20"/>
+    </row>
+    <row r="42" spans="1:18" ht="48" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
       <c r="B42" s="16">
         <f>ROW(B42) - ROW($B$7)</f>
         <v>35</v>
       </c>
-      <c r="C42" s="23" t="s">
+      <c r="C42" s="22" t="s">
         <v>17</v>
       </c>
       <c r="D42" s="14" t="s">
@@ -4307,214 +4155,210 @@
       <c r="H42" s="14" t="s">
         <v>284</v>
       </c>
-      <c r="I42" s="21" t="s">
-        <v>397</v>
+      <c r="I42" s="20" t="s">
+        <v>396</v>
       </c>
       <c r="J42" s="14" t="s">
         <v>325</v>
       </c>
       <c r="K42" s="14" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="L42" s="14">
         <v>2</v>
       </c>
       <c r="M42" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="N42" s="14">
         <v>30</v>
       </c>
-      <c r="O42" s="51" t="s">
-        <v>403</v>
+      <c r="O42" s="43" t="s">
+        <v>402</v>
       </c>
       <c r="P42" s="15">
         <v>6.3500000000000001E-2</v>
       </c>
       <c r="Q42" s="15">
-        <f>P42*N42</f>
+        <f t="shared" si="0"/>
         <v>1.905</v>
       </c>
       <c r="R42" s="14"/>
-      <c r="S42" s="20"/>
-    </row>
-    <row r="43" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43" spans="1:18" ht="36" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="B43" s="17">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="C43" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="D43" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="E43" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="F43" s="20" t="s">
+        <v>403</v>
+      </c>
+      <c r="G43" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="H43" s="20" t="s">
+        <v>285</v>
+      </c>
+      <c r="I43" s="20" t="s">
+        <v>396</v>
+      </c>
+      <c r="J43" s="20" t="s">
+        <v>326</v>
+      </c>
+      <c r="K43" s="14" t="s">
+        <v>396</v>
+      </c>
+      <c r="L43" s="20">
+        <v>1</v>
+      </c>
+      <c r="M43" s="14">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="N43" s="20">
+        <v>11</v>
+      </c>
+      <c r="O43" s="43" t="s">
+        <v>402</v>
+      </c>
+      <c r="P43" s="21">
+        <v>0.29949999999999999</v>
+      </c>
+      <c r="Q43" s="21">
         <f t="shared" si="0"/>
-        <v>36</v>
-      </c>
-      <c r="C43" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="D43" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="E43" s="21" t="s">
-        <v>136</v>
-      </c>
-      <c r="F43" s="21" t="s">
-        <v>404</v>
-      </c>
-      <c r="G43" s="21" t="s">
-        <v>192</v>
-      </c>
-      <c r="H43" s="21" t="s">
-        <v>285</v>
-      </c>
-      <c r="I43" s="21" t="s">
-        <v>397</v>
-      </c>
-      <c r="J43" s="21" t="s">
-        <v>326</v>
-      </c>
-      <c r="K43" s="14" t="s">
-        <v>397</v>
-      </c>
-      <c r="L43" s="21">
-        <v>1</v>
-      </c>
-      <c r="M43" s="14">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="N43" s="21">
-        <v>11</v>
-      </c>
-      <c r="O43" s="51" t="s">
-        <v>403</v>
-      </c>
-      <c r="P43" s="22">
-        <v>0.29949999999999999</v>
-      </c>
-      <c r="Q43" s="22">
-        <f>P43*N43</f>
         <v>3.2944999999999998</v>
       </c>
-      <c r="R43" s="21"/>
-      <c r="S43" s="21"/>
-    </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R43" s="20"/>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
       <c r="B44" s="16">
         <f>ROW(B44) - ROW($B$7)</f>
         <v>37</v>
       </c>
-      <c r="C44" s="23" t="s">
+      <c r="C44" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="D44" s="50" t="s">
+      <c r="D44" s="42" t="s">
         <v>68</v>
       </c>
-      <c r="E44" s="50" t="s">
+      <c r="E44" s="42" t="s">
         <v>137</v>
       </c>
-      <c r="F44" s="50" t="s">
-        <v>404</v>
-      </c>
-      <c r="G44" s="50" t="s">
+      <c r="F44" s="42" t="s">
+        <v>403</v>
+      </c>
+      <c r="G44" s="42" t="s">
         <v>193</v>
       </c>
-      <c r="H44" s="50" t="s">
-        <v>397</v>
-      </c>
-      <c r="I44" s="50" t="s">
-        <v>397</v>
-      </c>
-      <c r="J44" s="50" t="s">
-        <v>397</v>
-      </c>
-      <c r="K44" s="50" t="s">
-        <v>397</v>
-      </c>
-      <c r="L44" s="50">
+      <c r="H44" s="42" t="s">
+        <v>396</v>
+      </c>
+      <c r="I44" s="42" t="s">
+        <v>396</v>
+      </c>
+      <c r="J44" s="42" t="s">
+        <v>396</v>
+      </c>
+      <c r="K44" s="42" t="s">
+        <v>396</v>
+      </c>
+      <c r="L44" s="42">
         <v>4</v>
       </c>
-      <c r="M44" s="50">
-        <f t="shared" si="1"/>
+      <c r="M44" s="42">
+        <f t="shared" si="2"/>
         <v>40</v>
       </c>
-      <c r="N44" s="50" t="s">
-        <v>397</v>
+      <c r="N44" s="42" t="s">
+        <v>396</v>
       </c>
       <c r="O44" s="14" t="s">
-        <v>397</v>
-      </c>
-      <c r="P44" s="53" t="s">
-        <v>397</v>
-      </c>
-      <c r="Q44" s="53" t="s">
-        <v>397</v>
-      </c>
-      <c r="R44" s="55" t="s">
-        <v>408</v>
-      </c>
-      <c r="S44" s="54"/>
-    </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
+        <v>396</v>
+      </c>
+      <c r="P44" s="45" t="s">
+        <v>396</v>
+      </c>
+      <c r="Q44" s="45" t="s">
+        <v>396</v>
+      </c>
+      <c r="R44" s="46" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
       <c r="B45" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>38</v>
       </c>
-      <c r="C45" s="24" t="s">
+      <c r="C45" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="D45" s="21" t="s">
+      <c r="D45" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="E45" s="21" t="s">
+      <c r="E45" s="20" t="s">
         <v>138</v>
       </c>
-      <c r="F45" s="21" t="s">
+      <c r="F45" s="20" t="s">
         <v>194</v>
       </c>
-      <c r="G45" s="21" t="s">
+      <c r="G45" s="20" t="s">
         <v>239</v>
       </c>
-      <c r="H45" s="21" t="s">
+      <c r="H45" s="20" t="s">
         <v>272</v>
       </c>
-      <c r="I45" s="21" t="s">
-        <v>397</v>
-      </c>
-      <c r="J45" s="21" t="s">
+      <c r="I45" s="20" t="s">
+        <v>396</v>
+      </c>
+      <c r="J45" s="20" t="s">
         <v>327</v>
       </c>
       <c r="K45" s="14" t="s">
-        <v>397</v>
-      </c>
-      <c r="L45" s="21">
+        <v>396</v>
+      </c>
+      <c r="L45" s="20">
         <v>2</v>
       </c>
       <c r="M45" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="N45" s="21">
+      <c r="N45" s="20">
         <v>40</v>
       </c>
-      <c r="O45" s="51" t="s">
-        <v>403</v>
-      </c>
-      <c r="P45" s="22">
+      <c r="O45" s="43" t="s">
+        <v>402</v>
+      </c>
+      <c r="P45" s="21">
         <v>2.46E-2</v>
       </c>
-      <c r="Q45" s="22">
-        <f>P45*N45</f>
+      <c r="Q45" s="21">
+        <f t="shared" ref="Q45:Q77" si="3">P45*N45</f>
         <v>0.98399999999999999</v>
       </c>
-      <c r="R45" s="21"/>
-      <c r="S45" s="21"/>
-    </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R45" s="20"/>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="B46" s="16">
         <f>ROW(B46) - ROW($B$7)</f>
         <v>39</v>
       </c>
-      <c r="C46" s="23"/>
+      <c r="C46" s="22"/>
       <c r="D46" s="14" t="s">
         <v>70</v>
       </c>
@@ -4530,11 +4374,11 @@
       <c r="H46" s="14" t="s">
         <v>266</v>
       </c>
-      <c r="I46" s="21" t="s">
-        <v>397</v>
+      <c r="I46" s="20" t="s">
+        <v>396</v>
       </c>
       <c r="J46" s="14" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="K46" s="14" t="s">
         <v>368</v>
@@ -4543,88 +4387,86 @@
         <v>1</v>
       </c>
       <c r="M46" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="N46" s="14">
         <v>20</v>
       </c>
-      <c r="O46" s="51" t="s">
-        <v>403</v>
+      <c r="O46" s="43" t="s">
+        <v>402</v>
       </c>
       <c r="P46" s="15">
         <v>2.3099999999999999E-2</v>
       </c>
       <c r="Q46" s="15">
-        <f>P46*N46</f>
+        <f t="shared" si="3"/>
         <v>0.46199999999999997</v>
       </c>
       <c r="R46" s="14"/>
-      <c r="S46" s="20"/>
-    </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
       <c r="B47" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="C47" s="24" t="s">
+      <c r="C47" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="D47" s="21" t="s">
+      <c r="D47" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="E47" s="21" t="s">
+      <c r="E47" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="F47" s="21" t="s">
+      <c r="F47" s="20" t="s">
         <v>195</v>
       </c>
-      <c r="G47" s="21" t="s">
+      <c r="G47" s="20" t="s">
         <v>241</v>
       </c>
-      <c r="H47" s="21" t="s">
+      <c r="H47" s="20" t="s">
         <v>266</v>
       </c>
-      <c r="I47" s="21" t="s">
-        <v>397</v>
-      </c>
-      <c r="J47" s="21" t="s">
+      <c r="I47" s="20" t="s">
+        <v>396</v>
+      </c>
+      <c r="J47" s="20" t="s">
         <v>328</v>
       </c>
-      <c r="K47" s="21" t="s">
+      <c r="K47" s="20" t="s">
         <v>369</v>
       </c>
-      <c r="L47" s="21">
+      <c r="L47" s="20">
         <v>1</v>
       </c>
       <c r="M47" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="N47" s="21">
+      <c r="N47" s="20">
         <v>100</v>
       </c>
-      <c r="O47" s="51" t="s">
-        <v>403</v>
-      </c>
-      <c r="P47" s="22">
+      <c r="O47" s="43" t="s">
+        <v>402</v>
+      </c>
+      <c r="P47" s="21">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="Q47" s="22">
-        <f>P47*N47</f>
+      <c r="Q47" s="21">
+        <f t="shared" si="3"/>
         <v>0.12</v>
       </c>
-      <c r="R47" s="21"/>
-      <c r="S47" s="21"/>
-    </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R47" s="20"/>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
       <c r="B48" s="16">
         <f>ROW(B48) - ROW($B$7)</f>
         <v>41</v>
       </c>
-      <c r="C48" s="23" t="s">
+      <c r="C48" s="22" t="s">
         <v>21</v>
       </c>
       <c r="D48" s="14" t="s">
@@ -4642,8 +4484,8 @@
       <c r="H48" s="14" t="s">
         <v>266</v>
       </c>
-      <c r="I48" s="21" t="s">
-        <v>397</v>
+      <c r="I48" s="20" t="s">
+        <v>396</v>
       </c>
       <c r="J48" s="14" t="s">
         <v>329</v>
@@ -4655,88 +4497,86 @@
         <v>1</v>
       </c>
       <c r="M48" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="N48" s="14">
         <v>20</v>
       </c>
-      <c r="O48" s="51" t="s">
-        <v>403</v>
+      <c r="O48" s="43" t="s">
+        <v>402</v>
       </c>
       <c r="P48" s="15">
         <v>2.0799999999999999E-2</v>
       </c>
       <c r="Q48" s="15">
-        <f>P48*N48</f>
+        <f t="shared" si="3"/>
         <v>0.41599999999999998</v>
       </c>
       <c r="R48" s="14"/>
-      <c r="S48" s="20"/>
-    </row>
-    <row r="49" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+    </row>
+    <row r="49" spans="1:18" ht="24" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
       <c r="B49" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>42</v>
       </c>
-      <c r="C49" s="24" t="s">
+      <c r="C49" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="D49" s="21" t="s">
+      <c r="D49" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="E49" s="21" t="s">
+      <c r="E49" s="20" t="s">
         <v>142</v>
       </c>
-      <c r="F49" s="21" t="s">
+      <c r="F49" s="20" t="s">
         <v>195</v>
       </c>
-      <c r="G49" s="21" t="s">
+      <c r="G49" s="20" t="s">
         <v>243</v>
       </c>
-      <c r="H49" s="21" t="s">
+      <c r="H49" s="20" t="s">
         <v>266</v>
       </c>
-      <c r="I49" s="21" t="s">
-        <v>397</v>
-      </c>
-      <c r="J49" s="21" t="s">
+      <c r="I49" s="20" t="s">
+        <v>396</v>
+      </c>
+      <c r="J49" s="20" t="s">
         <v>330</v>
       </c>
-      <c r="K49" s="21" t="s">
+      <c r="K49" s="20" t="s">
         <v>371</v>
       </c>
-      <c r="L49" s="21">
+      <c r="L49" s="20">
         <v>12</v>
       </c>
       <c r="M49" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>120</v>
       </c>
-      <c r="N49" s="21">
+      <c r="N49" s="20">
         <v>200</v>
       </c>
-      <c r="O49" s="51" t="s">
-        <v>403</v>
-      </c>
-      <c r="P49" s="22">
+      <c r="O49" s="43" t="s">
+        <v>402</v>
+      </c>
+      <c r="P49" s="21">
         <v>1E-3</v>
       </c>
-      <c r="Q49" s="22">
-        <f>P49*N49</f>
+      <c r="Q49" s="21">
+        <f t="shared" si="3"/>
         <v>0.2</v>
       </c>
-      <c r="R49" s="21"/>
-      <c r="S49" s="21"/>
-    </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R49" s="20"/>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
       <c r="B50" s="16">
         <f>ROW(B50) - ROW($B$7)</f>
         <v>43</v>
       </c>
-      <c r="C50" s="23" t="s">
+      <c r="C50" s="22" t="s">
         <v>21</v>
       </c>
       <c r="D50" s="14" t="s">
@@ -4754,8 +4594,8 @@
       <c r="H50" s="14" t="s">
         <v>266</v>
       </c>
-      <c r="I50" s="21" t="s">
-        <v>397</v>
+      <c r="I50" s="20" t="s">
+        <v>396</v>
       </c>
       <c r="J50" s="14" t="s">
         <v>331</v>
@@ -4767,86 +4607,84 @@
         <v>2</v>
       </c>
       <c r="M50" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="N50" s="14">
         <v>100</v>
       </c>
-      <c r="O50" s="51" t="s">
-        <v>403</v>
+      <c r="O50" s="43" t="s">
+        <v>402</v>
       </c>
       <c r="P50" s="15">
         <v>5.9999999999999995E-4</v>
       </c>
       <c r="Q50" s="15">
-        <f>P50*N50</f>
+        <f t="shared" si="3"/>
         <v>0.06</v>
       </c>
       <c r="R50" s="14"/>
-      <c r="S50" s="20"/>
-    </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
       <c r="B51" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>44</v>
       </c>
-      <c r="C51" s="24" t="s">
+      <c r="C51" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="D51" s="21" t="s">
+      <c r="D51" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="E51" s="21" t="s">
+      <c r="E51" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="F51" s="21" t="s">
+      <c r="F51" s="20" t="s">
         <v>195</v>
       </c>
-      <c r="G51" s="21" t="s">
+      <c r="G51" s="20" t="s">
         <v>245</v>
       </c>
-      <c r="H51" s="21" t="s">
+      <c r="H51" s="20" t="s">
         <v>266</v>
       </c>
-      <c r="I51" s="21"/>
-      <c r="J51" s="21" t="s">
+      <c r="I51" s="20"/>
+      <c r="J51" s="20" t="s">
         <v>332</v>
       </c>
-      <c r="K51" s="21" t="s">
+      <c r="K51" s="20" t="s">
         <v>373</v>
       </c>
-      <c r="L51" s="21">
+      <c r="L51" s="20">
         <v>8</v>
       </c>
       <c r="M51" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>80</v>
       </c>
-      <c r="N51" s="21">
+      <c r="N51" s="20">
         <v>100</v>
       </c>
-      <c r="O51" s="51" t="s">
-        <v>403</v>
-      </c>
-      <c r="P51" s="22">
+      <c r="O51" s="43" t="s">
+        <v>402</v>
+      </c>
+      <c r="P51" s="21">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="Q51" s="22">
-        <f>P51*N51</f>
+      <c r="Q51" s="21">
+        <f t="shared" si="3"/>
         <v>0.12</v>
       </c>
-      <c r="R51" s="21"/>
-      <c r="S51" s="21"/>
-    </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R51" s="20"/>
+    </row>
+    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
       <c r="B52" s="16">
         <f>ROW(B52) - ROW($B$7)</f>
         <v>45</v>
       </c>
-      <c r="C52" s="23" t="s">
+      <c r="C52" s="22" t="s">
         <v>21</v>
       </c>
       <c r="D52" s="14" t="s">
@@ -4875,86 +4713,84 @@
         <v>2</v>
       </c>
       <c r="M52" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="N52" s="14">
         <v>100</v>
       </c>
-      <c r="O52" s="51" t="s">
-        <v>403</v>
+      <c r="O52" s="43" t="s">
+        <v>402</v>
       </c>
       <c r="P52" s="15">
         <v>8.9999999999999998E-4</v>
       </c>
       <c r="Q52" s="15">
-        <f>P52*N52</f>
+        <f t="shared" si="3"/>
         <v>0.09</v>
       </c>
       <c r="R52" s="14"/>
-      <c r="S52" s="20"/>
-    </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
       <c r="B53" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>46</v>
       </c>
-      <c r="C53" s="23" t="s">
+      <c r="C53" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="D53" s="21" t="s">
+      <c r="D53" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="E53" s="21" t="s">
+      <c r="E53" s="20" t="s">
         <v>146</v>
       </c>
-      <c r="F53" s="21" t="s">
+      <c r="F53" s="20" t="s">
         <v>195</v>
       </c>
-      <c r="G53" s="21" t="s">
+      <c r="G53" s="20" t="s">
         <v>247</v>
       </c>
-      <c r="H53" s="21" t="s">
+      <c r="H53" s="20" t="s">
         <v>266</v>
       </c>
-      <c r="I53" s="21"/>
-      <c r="J53" s="21" t="s">
+      <c r="I53" s="20"/>
+      <c r="J53" s="20" t="s">
         <v>334</v>
       </c>
-      <c r="K53" s="21" t="s">
+      <c r="K53" s="20" t="s">
         <v>375</v>
       </c>
-      <c r="L53" s="21">
+      <c r="L53" s="20">
         <v>4</v>
       </c>
       <c r="M53" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>40</v>
       </c>
-      <c r="N53" s="21">
+      <c r="N53" s="20">
         <v>100</v>
       </c>
-      <c r="O53" s="51" t="s">
-        <v>403</v>
-      </c>
-      <c r="P53" s="22">
+      <c r="O53" s="43" t="s">
+        <v>402</v>
+      </c>
+      <c r="P53" s="21">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="Q53" s="22">
-        <f>P53*N53</f>
+      <c r="Q53" s="21">
+        <f t="shared" si="3"/>
         <v>0.13</v>
       </c>
-      <c r="R53" s="21"/>
-      <c r="S53" s="21"/>
-    </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R53" s="20"/>
+    </row>
+    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
       <c r="B54" s="16">
         <f>ROW(B54) - ROW($B$7)</f>
         <v>47</v>
       </c>
-      <c r="C54" s="23" t="s">
+      <c r="C54" s="22" t="s">
         <v>21</v>
       </c>
       <c r="D54" s="14" t="s">
@@ -4966,17 +4802,17 @@
       <c r="F54" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="G54" s="50" t="s">
+      <c r="G54" s="42" t="s">
         <v>248</v>
       </c>
       <c r="H54" s="14" t="s">
         <v>266</v>
       </c>
       <c r="I54" s="14" t="s">
+        <v>410</v>
+      </c>
+      <c r="J54" s="14" t="s">
         <v>411</v>
-      </c>
-      <c r="J54" s="14" t="s">
-        <v>412</v>
       </c>
       <c r="K54" s="14" t="s">
         <v>376</v>
@@ -4985,88 +4821,86 @@
         <v>1</v>
       </c>
       <c r="M54" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="N54" s="14">
         <v>100</v>
       </c>
-      <c r="O54" s="51" t="s">
-        <v>403</v>
+      <c r="O54" s="43" t="s">
+        <v>402</v>
       </c>
       <c r="P54" s="15">
         <v>2E-3</v>
       </c>
       <c r="Q54" s="15">
-        <f>P54*N54</f>
+        <f t="shared" si="3"/>
         <v>0.2</v>
       </c>
       <c r="R54" s="14"/>
-      <c r="S54" s="20"/>
-    </row>
-    <row r="55" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="55" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
       <c r="B55" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>48</v>
       </c>
-      <c r="C55" s="24" t="s">
+      <c r="C55" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D55" s="21" t="s">
+      <c r="D55" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="E55" s="21" t="s">
+      <c r="E55" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="F55" s="21" t="s">
+      <c r="F55" s="20" t="s">
         <v>198</v>
       </c>
-      <c r="G55" s="56" t="s">
+      <c r="G55" s="47" t="s">
         <v>249</v>
       </c>
-      <c r="H55" s="21" t="s">
+      <c r="H55" s="20" t="s">
         <v>286</v>
       </c>
-      <c r="I55" s="21" t="s">
-        <v>414</v>
-      </c>
-      <c r="J55" s="21" t="s">
+      <c r="I55" s="20" t="s">
         <v>413</v>
       </c>
-      <c r="K55" s="21" t="s">
+      <c r="J55" s="20" t="s">
+        <v>412</v>
+      </c>
+      <c r="K55" s="20" t="s">
         <v>377</v>
       </c>
-      <c r="L55" s="21">
+      <c r="L55" s="20">
         <v>2</v>
       </c>
       <c r="M55" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="N55" s="21">
+      <c r="N55" s="20">
         <v>25</v>
       </c>
-      <c r="O55" s="51" t="s">
-        <v>403</v>
-      </c>
-      <c r="P55" s="22">
+      <c r="O55" s="43" t="s">
+        <v>402</v>
+      </c>
+      <c r="P55" s="21">
         <v>8.0100000000000005E-2</v>
       </c>
-      <c r="Q55" s="22">
-        <f>P55*N55</f>
+      <c r="Q55" s="21">
+        <f t="shared" si="3"/>
         <v>2.0024999999999999</v>
       </c>
-      <c r="R55" s="21"/>
-      <c r="S55" s="21"/>
-    </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R55" s="20"/>
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
       <c r="B56" s="16">
         <f>ROW(B56) - ROW($B$7)</f>
         <v>49</v>
       </c>
-      <c r="C56" s="24" t="s">
+      <c r="C56" s="23" t="s">
         <v>21</v>
       </c>
       <c r="D56" s="14" t="s">
@@ -5095,86 +4929,84 @@
         <v>2</v>
       </c>
       <c r="M56" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="N56" s="14">
         <v>100</v>
       </c>
-      <c r="O56" s="51" t="s">
-        <v>403</v>
+      <c r="O56" s="43" t="s">
+        <v>402</v>
       </c>
       <c r="P56" s="15">
         <v>1.1999999999999999E-3</v>
       </c>
       <c r="Q56" s="15">
-        <f>P56*N56</f>
+        <f t="shared" si="3"/>
         <v>0.12</v>
       </c>
       <c r="R56" s="14"/>
-      <c r="S56" s="20"/>
-    </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
       <c r="B57" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="C57" s="24" t="s">
+      <c r="C57" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="D57" s="21" t="s">
+      <c r="D57" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="E57" s="21" t="s">
+      <c r="E57" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="F57" s="21" t="s">
+      <c r="F57" s="20" t="s">
         <v>195</v>
       </c>
-      <c r="G57" s="21" t="s">
+      <c r="G57" s="20" t="s">
         <v>251</v>
       </c>
-      <c r="H57" s="21" t="s">
+      <c r="H57" s="20" t="s">
         <v>266</v>
       </c>
-      <c r="I57" s="21"/>
-      <c r="J57" s="21" t="s">
+      <c r="I57" s="20"/>
+      <c r="J57" s="20" t="s">
         <v>336</v>
       </c>
-      <c r="K57" s="21" t="s">
+      <c r="K57" s="20" t="s">
         <v>379</v>
       </c>
-      <c r="L57" s="21">
+      <c r="L57" s="20">
         <v>4</v>
       </c>
       <c r="M57" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>40</v>
       </c>
-      <c r="N57" s="21">
+      <c r="N57" s="20">
         <v>60</v>
       </c>
-      <c r="O57" s="51" t="s">
-        <v>403</v>
-      </c>
-      <c r="P57" s="22">
+      <c r="O57" s="43" t="s">
+        <v>402</v>
+      </c>
+      <c r="P57" s="21">
         <v>2.0899999999999998E-2</v>
       </c>
-      <c r="Q57" s="22">
-        <f>P57*N57</f>
+      <c r="Q57" s="21">
+        <f t="shared" si="3"/>
         <v>1.254</v>
       </c>
-      <c r="R57" s="21"/>
-      <c r="S57" s="21"/>
-    </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R57" s="20"/>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A58" s="1"/>
       <c r="B58" s="16">
         <f>ROW(B58) - ROW($B$7)</f>
         <v>51</v>
       </c>
-      <c r="C58" s="23" t="s">
+      <c r="C58" s="22" t="s">
         <v>21</v>
       </c>
       <c r="D58" s="14" t="s">
@@ -5203,88 +5035,86 @@
         <v>1</v>
       </c>
       <c r="M58" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="N58" s="14">
         <v>15</v>
       </c>
-      <c r="O58" s="51" t="s">
-        <v>403</v>
+      <c r="O58" s="43" t="s">
+        <v>402</v>
       </c>
       <c r="P58" s="15">
         <v>0.13650000000000001</v>
       </c>
       <c r="Q58" s="15">
-        <f>P58*N58</f>
+        <f t="shared" si="3"/>
         <v>2.0475000000000003</v>
       </c>
       <c r="R58" s="14"/>
-      <c r="S58" s="20"/>
-    </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
       <c r="B59" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>52</v>
       </c>
-      <c r="C59" s="24" t="s">
+      <c r="C59" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="D59" s="21" t="s">
+      <c r="D59" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="E59" s="21" t="s">
+      <c r="E59" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="F59" s="21" t="s">
+      <c r="F59" s="20" t="s">
         <v>195</v>
       </c>
-      <c r="G59" s="56" t="s">
+      <c r="G59" s="47" t="s">
         <v>253</v>
       </c>
-      <c r="H59" s="21" t="s">
+      <c r="H59" s="20" t="s">
         <v>266</v>
       </c>
-      <c r="I59" s="21" t="s">
-        <v>416</v>
-      </c>
-      <c r="J59" s="21" t="s">
+      <c r="I59" s="20" t="s">
         <v>415</v>
       </c>
-      <c r="K59" s="21" t="s">
+      <c r="J59" s="20" t="s">
+        <v>414</v>
+      </c>
+      <c r="K59" s="20" t="s">
         <v>381</v>
       </c>
-      <c r="L59" s="21">
+      <c r="L59" s="20">
         <v>3</v>
       </c>
       <c r="M59" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="N59" s="21">
+      <c r="N59" s="20">
         <v>100</v>
       </c>
-      <c r="O59" s="51" t="s">
-        <v>403</v>
-      </c>
-      <c r="P59" s="22">
+      <c r="O59" s="43" t="s">
+        <v>402</v>
+      </c>
+      <c r="P59" s="21">
         <v>1E-3</v>
       </c>
-      <c r="Q59" s="22">
-        <f>P59*N59</f>
+      <c r="Q59" s="21">
+        <f t="shared" si="3"/>
         <v>0.1</v>
       </c>
-      <c r="R59" s="21"/>
-      <c r="S59" s="21"/>
-    </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R59" s="20"/>
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
       <c r="B60" s="16">
         <f>ROW(B60) - ROW($B$7)</f>
         <v>53</v>
       </c>
-      <c r="C60" s="23" t="s">
+      <c r="C60" s="22" t="s">
         <v>21</v>
       </c>
       <c r="D60" s="14" t="s">
@@ -5303,7 +5133,7 @@
         <v>266</v>
       </c>
       <c r="I60" s="14" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="J60" s="14" t="s">
         <v>338</v>
@@ -5315,86 +5145,84 @@
         <v>2</v>
       </c>
       <c r="M60" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="N60" s="14">
         <v>100</v>
       </c>
-      <c r="O60" s="51" t="s">
-        <v>403</v>
+      <c r="O60" s="43" t="s">
+        <v>402</v>
       </c>
       <c r="P60" s="15">
         <v>1.1999999999999999E-3</v>
       </c>
       <c r="Q60" s="15">
-        <f>P60*N60</f>
+        <f t="shared" si="3"/>
         <v>0.12</v>
       </c>
       <c r="R60" s="14"/>
-      <c r="S60" s="20"/>
-    </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
       <c r="B61" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>54</v>
       </c>
-      <c r="C61" s="24" t="s">
+      <c r="C61" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="D61" s="21" t="s">
+      <c r="D61" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="E61" s="21" t="s">
+      <c r="E61" s="20" t="s">
         <v>154</v>
       </c>
-      <c r="F61" s="21" t="s">
+      <c r="F61" s="20" t="s">
         <v>195</v>
       </c>
-      <c r="G61" s="21" t="s">
+      <c r="G61" s="20" t="s">
         <v>255</v>
       </c>
-      <c r="H61" s="21" t="s">
+      <c r="H61" s="20" t="s">
         <v>266</v>
       </c>
-      <c r="I61" s="21"/>
-      <c r="J61" s="21" t="s">
+      <c r="I61" s="20"/>
+      <c r="J61" s="20" t="s">
         <v>339</v>
       </c>
-      <c r="K61" s="21" t="s">
+      <c r="K61" s="20" t="s">
         <v>383</v>
       </c>
-      <c r="L61" s="21">
+      <c r="L61" s="20">
         <v>1</v>
       </c>
       <c r="M61" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="N61" s="21">
+      <c r="N61" s="20">
         <v>100</v>
       </c>
-      <c r="O61" s="51" t="s">
-        <v>403</v>
-      </c>
-      <c r="P61" s="22">
+      <c r="O61" s="43" t="s">
+        <v>402</v>
+      </c>
+      <c r="P61" s="21">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="Q61" s="22">
-        <f>P61*N61</f>
+      <c r="Q61" s="21">
+        <f t="shared" si="3"/>
         <v>0.12</v>
       </c>
-      <c r="R61" s="21"/>
-      <c r="S61" s="21"/>
-    </row>
-    <row r="62" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+      <c r="R61" s="20"/>
+    </row>
+    <row r="62" spans="1:18" ht="48" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
       <c r="B62" s="16">
         <f>ROW(B62) - ROW($B$7)</f>
         <v>55</v>
       </c>
-      <c r="C62" s="23" t="s">
+      <c r="C62" s="22" t="s">
         <v>23</v>
       </c>
       <c r="D62" s="14" t="s">
@@ -5404,7 +5232,7 @@
         <v>155</v>
       </c>
       <c r="F62" s="14" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="G62" s="14" t="s">
         <v>199</v>
@@ -5417,94 +5245,92 @@
         <v>340</v>
       </c>
       <c r="K62" s="14" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="L62" s="14">
         <v>2</v>
       </c>
       <c r="M62" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="N62" s="14">
         <v>40</v>
       </c>
-      <c r="O62" s="51" t="s">
-        <v>403</v>
+      <c r="O62" s="43" t="s">
+        <v>402</v>
       </c>
       <c r="P62" s="15">
         <v>1.9699999999999999E-2</v>
       </c>
       <c r="Q62" s="15">
-        <f>P62*N62</f>
+        <f t="shared" si="3"/>
         <v>0.78799999999999992</v>
       </c>
       <c r="R62" s="14"/>
-      <c r="S62" s="20"/>
-    </row>
-    <row r="63" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
       <c r="B63" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>56</v>
       </c>
-      <c r="C63" s="24" t="s">
+      <c r="C63" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="D63" s="21" t="s">
+      <c r="D63" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="E63" s="21" t="s">
+      <c r="E63" s="20" t="s">
         <v>156</v>
       </c>
       <c r="F63" s="14" t="s">
-        <v>404</v>
-      </c>
-      <c r="G63" s="21" t="s">
+        <v>403</v>
+      </c>
+      <c r="G63" s="20" t="s">
         <v>200</v>
       </c>
-      <c r="H63" s="21" t="s">
+      <c r="H63" s="20" t="s">
         <v>288</v>
       </c>
-      <c r="I63" s="21" t="s">
-        <v>397</v>
-      </c>
-      <c r="J63" s="21" t="s">
-        <v>397</v>
+      <c r="I63" s="20" t="s">
+        <v>396</v>
+      </c>
+      <c r="J63" s="20" t="s">
+        <v>396</v>
       </c>
       <c r="K63" s="14" t="s">
-        <v>397</v>
-      </c>
-      <c r="L63" s="21">
+        <v>396</v>
+      </c>
+      <c r="L63" s="20">
         <v>1</v>
       </c>
       <c r="M63" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="N63" s="21">
+      <c r="N63" s="20">
         <v>11</v>
       </c>
-      <c r="O63" s="51" t="s">
-        <v>422</v>
-      </c>
-      <c r="P63" s="22">
+      <c r="O63" s="43" t="s">
+        <v>421</v>
+      </c>
+      <c r="P63" s="21">
         <v>36.279000000000003</v>
       </c>
-      <c r="Q63" s="22">
-        <f>P63*N63</f>
+      <c r="Q63" s="21">
+        <f t="shared" si="3"/>
         <v>399.06900000000002</v>
       </c>
-      <c r="R63" s="21"/>
-      <c r="S63" s="21"/>
-    </row>
-    <row r="64" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+      <c r="R63" s="20"/>
+    </row>
+    <row r="64" spans="1:18" ht="48" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
       <c r="B64" s="16">
         <f>ROW(B64) - ROW($B$7)</f>
         <v>57</v>
       </c>
-      <c r="C64" s="23" t="s">
+      <c r="C64" s="22" t="s">
         <v>25</v>
       </c>
       <c r="D64" s="14" t="s">
@@ -5514,7 +5340,7 @@
         <v>157</v>
       </c>
       <c r="F64" s="14" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="G64" s="14" t="s">
         <v>256</v>
@@ -5527,92 +5353,90 @@
         <v>341</v>
       </c>
       <c r="K64" s="14" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="L64" s="14">
         <v>1</v>
       </c>
       <c r="M64" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="N64" s="14">
         <v>11</v>
       </c>
-      <c r="O64" s="51" t="s">
-        <v>403</v>
+      <c r="O64" s="43" t="s">
+        <v>402</v>
       </c>
       <c r="P64" s="15">
         <v>0.26490000000000002</v>
       </c>
       <c r="Q64" s="15">
-        <f>P64*N64</f>
+        <f t="shared" si="3"/>
         <v>2.9139000000000004</v>
       </c>
       <c r="R64" s="14"/>
-      <c r="S64" s="20"/>
-    </row>
-    <row r="65" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="65" spans="1:18" ht="48" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
       <c r="B65" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>58</v>
       </c>
-      <c r="C65" s="24" t="s">
+      <c r="C65" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="D65" s="21" t="s">
+      <c r="D65" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="E65" s="21" t="s">
+      <c r="E65" s="20" t="s">
         <v>158</v>
       </c>
       <c r="F65" s="14" t="s">
-        <v>404</v>
-      </c>
-      <c r="G65" s="21" t="s">
+        <v>403</v>
+      </c>
+      <c r="G65" s="20" t="s">
         <v>201</v>
       </c>
-      <c r="H65" s="21" t="s">
+      <c r="H65" s="20" t="s">
         <v>289</v>
       </c>
-      <c r="I65" s="21"/>
-      <c r="J65" s="21" t="s">
+      <c r="I65" s="20"/>
+      <c r="J65" s="20" t="s">
         <v>342</v>
       </c>
       <c r="K65" s="14" t="s">
-        <v>397</v>
-      </c>
-      <c r="L65" s="21">
+        <v>396</v>
+      </c>
+      <c r="L65" s="20">
         <v>1</v>
       </c>
       <c r="M65" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="N65" s="21">
+      <c r="N65" s="20">
         <v>15</v>
       </c>
-      <c r="O65" s="51" t="s">
-        <v>403</v>
-      </c>
-      <c r="P65" s="22">
+      <c r="O65" s="43" t="s">
+        <v>402</v>
+      </c>
+      <c r="P65" s="21">
         <v>7.6499999999999999E-2</v>
       </c>
-      <c r="Q65" s="22">
-        <f>P65*N65</f>
+      <c r="Q65" s="21">
+        <f t="shared" si="3"/>
         <v>1.1475</v>
       </c>
-      <c r="R65" s="21"/>
-      <c r="S65" s="21"/>
-    </row>
-    <row r="66" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+      <c r="R65" s="20"/>
+    </row>
+    <row r="66" spans="1:18" ht="36" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
       <c r="B66" s="16">
         <f>ROW(B66) - ROW($B$7)</f>
         <v>59</v>
       </c>
-      <c r="C66" s="23" t="s">
+      <c r="C66" s="22" t="s">
         <v>26</v>
       </c>
       <c r="D66" s="14" t="s">
@@ -5622,7 +5446,7 @@
         <v>159</v>
       </c>
       <c r="F66" s="14" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="G66" s="14" t="s">
         <v>202</v>
@@ -5635,92 +5459,90 @@
         <v>343</v>
       </c>
       <c r="K66" s="14" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="L66" s="14">
         <v>1</v>
       </c>
       <c r="M66" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="N66" s="14">
         <v>20</v>
       </c>
-      <c r="O66" s="51" t="s">
-        <v>403</v>
+      <c r="O66" s="43" t="s">
+        <v>402</v>
       </c>
       <c r="P66" s="15">
         <v>4.1500000000000002E-2</v>
       </c>
       <c r="Q66" s="15">
-        <f>P66*N66</f>
+        <f t="shared" si="3"/>
         <v>0.83000000000000007</v>
       </c>
       <c r="R66" s="14"/>
-      <c r="S66" s="20"/>
-    </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
       <c r="B67" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>60</v>
       </c>
-      <c r="C67" s="24" t="s">
+      <c r="C67" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="D67" s="21" t="s">
+      <c r="D67" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="E67" s="21" t="s">
+      <c r="E67" s="20" t="s">
         <v>160</v>
       </c>
-      <c r="F67" s="21" t="s">
+      <c r="F67" s="20" t="s">
         <v>203</v>
       </c>
-      <c r="G67" s="21" t="s">
+      <c r="G67" s="20" t="s">
         <v>257</v>
       </c>
-      <c r="H67" s="21" t="s">
+      <c r="H67" s="20" t="s">
         <v>290</v>
       </c>
-      <c r="I67" s="21"/>
-      <c r="J67" s="21" t="s">
+      <c r="I67" s="20"/>
+      <c r="J67" s="20" t="s">
         <v>344</v>
       </c>
       <c r="K67" s="14" t="s">
-        <v>397</v>
-      </c>
-      <c r="L67" s="21">
+        <v>396</v>
+      </c>
+      <c r="L67" s="20">
         <v>1</v>
       </c>
       <c r="M67" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="N67" s="21">
+      <c r="N67" s="20">
         <v>11</v>
       </c>
-      <c r="O67" s="51" t="s">
-        <v>403</v>
-      </c>
-      <c r="P67" s="22">
+      <c r="O67" s="43" t="s">
+        <v>402</v>
+      </c>
+      <c r="P67" s="21">
         <v>0.49390000000000001</v>
       </c>
-      <c r="Q67" s="22">
-        <f>P67*N67</f>
+      <c r="Q67" s="21">
+        <f t="shared" si="3"/>
         <v>5.4329000000000001</v>
       </c>
-      <c r="R67" s="21"/>
-      <c r="S67" s="21"/>
-    </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R67" s="20"/>
+    </row>
+    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
       <c r="B68" s="16">
         <f>ROW(B68) - ROW($B$7)</f>
         <v>61</v>
       </c>
-      <c r="C68" s="23" t="s">
+      <c r="C68" s="22" t="s">
         <v>27</v>
       </c>
       <c r="D68" s="14" t="s">
@@ -5743,92 +5565,90 @@
         <v>345</v>
       </c>
       <c r="K68" s="14" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="L68" s="14">
         <v>1</v>
       </c>
       <c r="M68" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="N68" s="14">
         <v>15</v>
       </c>
-      <c r="O68" s="51" t="s">
-        <v>403</v>
+      <c r="O68" s="43" t="s">
+        <v>402</v>
       </c>
       <c r="P68" s="15">
         <v>0.17169999999999999</v>
       </c>
       <c r="Q68" s="15">
-        <f>P68*N68</f>
+        <f t="shared" si="3"/>
         <v>2.5754999999999999</v>
       </c>
       <c r="R68" s="14"/>
-      <c r="S68" s="20"/>
-    </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A69" s="1"/>
       <c r="B69" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>62</v>
       </c>
-      <c r="C69" s="24" t="s">
+      <c r="C69" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="D69" s="21" t="s">
+      <c r="D69" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="E69" s="21" t="s">
+      <c r="E69" s="20" t="s">
         <v>162</v>
       </c>
-      <c r="F69" s="21" t="s">
+      <c r="F69" s="20" t="s">
         <v>205</v>
       </c>
-      <c r="G69" s="21" t="s">
+      <c r="G69" s="20" t="s">
         <v>259</v>
       </c>
-      <c r="H69" s="21" t="s">
+      <c r="H69" s="20" t="s">
         <v>292</v>
       </c>
-      <c r="I69" s="21"/>
-      <c r="J69" s="21" t="s">
+      <c r="I69" s="20"/>
+      <c r="J69" s="20" t="s">
         <v>346</v>
       </c>
       <c r="K69" s="14" t="s">
-        <v>397</v>
-      </c>
-      <c r="L69" s="21">
+        <v>396</v>
+      </c>
+      <c r="L69" s="20">
         <v>1</v>
       </c>
       <c r="M69" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="N69" s="21">
+      <c r="N69" s="20">
         <v>11</v>
       </c>
-      <c r="O69" s="51" t="s">
-        <v>403</v>
-      </c>
-      <c r="P69" s="22">
+      <c r="O69" s="43" t="s">
+        <v>402</v>
+      </c>
+      <c r="P69" s="21">
         <v>4.3540999999999999</v>
       </c>
-      <c r="Q69" s="22">
-        <f>P69*N69</f>
+      <c r="Q69" s="21">
+        <f t="shared" si="3"/>
         <v>47.895099999999999</v>
       </c>
-      <c r="R69" s="21"/>
-      <c r="S69" s="21"/>
-    </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R69" s="20"/>
+    </row>
+    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
       <c r="B70" s="16">
         <f>ROW(B70) - ROW($B$7)</f>
         <v>63</v>
       </c>
-      <c r="C70" s="23" t="s">
+      <c r="C70" s="22" t="s">
         <v>27</v>
       </c>
       <c r="D70" s="14" t="s">
@@ -5851,92 +5671,90 @@
         <v>347</v>
       </c>
       <c r="K70" s="14" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="L70" s="14">
         <v>1</v>
       </c>
       <c r="M70" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="N70" s="14">
         <v>11</v>
       </c>
-      <c r="O70" s="51" t="s">
-        <v>403</v>
+      <c r="O70" s="43" t="s">
+        <v>402</v>
       </c>
       <c r="P70" s="15">
         <v>4.0083000000000002</v>
       </c>
       <c r="Q70" s="15">
-        <f>P70*N70</f>
+        <f t="shared" si="3"/>
         <v>44.091300000000004</v>
       </c>
       <c r="R70" s="14"/>
-      <c r="S70" s="20"/>
-    </row>
-    <row r="71" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="71" spans="1:18" ht="24" x14ac:dyDescent="0.25">
       <c r="A71" s="1"/>
       <c r="B71" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>64</v>
       </c>
-      <c r="C71" s="24" t="s">
+      <c r="C71" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="D71" s="21" t="s">
+      <c r="D71" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="E71" s="21" t="s">
+      <c r="E71" s="20" t="s">
         <v>164</v>
       </c>
-      <c r="F71" s="21" t="s">
+      <c r="F71" s="20" t="s">
         <v>207</v>
       </c>
-      <c r="G71" s="21" t="s">
+      <c r="G71" s="20" t="s">
         <v>261</v>
       </c>
-      <c r="H71" s="21" t="s">
+      <c r="H71" s="20" t="s">
         <v>294</v>
       </c>
-      <c r="I71" s="21"/>
-      <c r="J71" s="21" t="s">
+      <c r="I71" s="20"/>
+      <c r="J71" s="20" t="s">
         <v>348</v>
       </c>
       <c r="K71" s="14" t="s">
-        <v>397</v>
-      </c>
-      <c r="L71" s="21">
+        <v>396</v>
+      </c>
+      <c r="L71" s="20">
         <v>4</v>
       </c>
       <c r="M71" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>40</v>
       </c>
-      <c r="N71" s="21">
+      <c r="N71" s="20">
         <v>41</v>
       </c>
-      <c r="O71" s="51" t="s">
-        <v>422</v>
-      </c>
-      <c r="P71" s="22">
+      <c r="O71" s="43" t="s">
+        <v>421</v>
+      </c>
+      <c r="P71" s="21">
         <v>0.81884999999999997</v>
       </c>
-      <c r="Q71" s="22">
-        <f>P71*N71</f>
+      <c r="Q71" s="21">
+        <f t="shared" si="3"/>
         <v>33.572849999999995</v>
       </c>
-      <c r="R71" s="21"/>
-      <c r="S71" s="21"/>
-    </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R71" s="20"/>
+    </row>
+    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A72" s="1"/>
       <c r="B72" s="16">
         <f>ROW(B72) - ROW($B$7)</f>
         <v>65</v>
       </c>
-      <c r="C72" s="23" t="s">
+      <c r="C72" s="22" t="s">
         <v>27</v>
       </c>
       <c r="D72" s="14" t="s">
@@ -5959,92 +5777,90 @@
         <v>349</v>
       </c>
       <c r="K72" s="14" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="L72" s="14">
         <v>1</v>
       </c>
       <c r="M72" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="N72" s="14">
         <v>15</v>
       </c>
-      <c r="O72" s="51" t="s">
-        <v>403</v>
+      <c r="O72" s="43" t="s">
+        <v>402</v>
       </c>
       <c r="P72" s="15">
         <v>0.21360000000000001</v>
       </c>
       <c r="Q72" s="15">
-        <f>P72*N72</f>
+        <f t="shared" si="3"/>
         <v>3.2040000000000002</v>
       </c>
       <c r="R72" s="14"/>
-      <c r="S72" s="20"/>
-    </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
       <c r="B73" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>66</v>
       </c>
-      <c r="C73" s="24" t="s">
+      <c r="C73" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="D73" s="21" t="s">
+      <c r="D73" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="E73" s="21" t="s">
+      <c r="E73" s="20" t="s">
         <v>166</v>
       </c>
-      <c r="F73" s="21" t="s">
+      <c r="F73" s="20" t="s">
         <v>209</v>
       </c>
-      <c r="G73" s="21" t="s">
+      <c r="G73" s="20" t="s">
         <v>263</v>
       </c>
-      <c r="H73" s="21" t="s">
+      <c r="H73" s="20" t="s">
         <v>290</v>
       </c>
-      <c r="I73" s="21"/>
-      <c r="J73" s="21" t="s">
+      <c r="I73" s="20"/>
+      <c r="J73" s="20" t="s">
         <v>350</v>
       </c>
       <c r="K73" s="14" t="s">
-        <v>397</v>
-      </c>
-      <c r="L73" s="21">
+        <v>396</v>
+      </c>
+      <c r="L73" s="20">
         <v>1</v>
       </c>
       <c r="M73" s="14">
-        <f t="shared" ref="M73:M76" si="2">L73*10</f>
+        <f t="shared" ref="M73:M77" si="4">L73*10</f>
         <v>10</v>
       </c>
-      <c r="N73" s="21">
+      <c r="N73" s="20">
         <v>11</v>
       </c>
-      <c r="O73" s="51" t="s">
-        <v>403</v>
-      </c>
-      <c r="P73" s="22">
+      <c r="O73" s="43" t="s">
+        <v>402</v>
+      </c>
+      <c r="P73" s="21">
         <v>0.52639999999999998</v>
       </c>
-      <c r="Q73" s="22">
-        <f>P73*N73</f>
+      <c r="Q73" s="21">
+        <f t="shared" si="3"/>
         <v>5.7904</v>
       </c>
-      <c r="R73" s="21"/>
-      <c r="S73" s="21"/>
-    </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R73" s="20"/>
+    </row>
+    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
       <c r="B74" s="16">
         <f>ROW(B74) - ROW($B$7)</f>
         <v>67</v>
       </c>
-      <c r="C74" s="23" t="s">
+      <c r="C74" s="22" t="s">
         <v>30</v>
       </c>
       <c r="D74" s="14" t="s">
@@ -6067,164 +5883,190 @@
         <v>351</v>
       </c>
       <c r="K74" s="14" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="L74" s="14">
         <v>1</v>
       </c>
       <c r="M74" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>10</v>
       </c>
       <c r="N74" s="14">
         <v>15</v>
       </c>
-      <c r="O74" s="51" t="s">
-        <v>403</v>
+      <c r="O74" s="43" t="s">
+        <v>402</v>
       </c>
       <c r="P74" s="15">
         <v>0.29930000000000001</v>
       </c>
       <c r="Q74" s="15">
-        <f>P74*N74</f>
+        <f t="shared" si="3"/>
         <v>4.4895000000000005</v>
       </c>
       <c r="R74" s="14"/>
-      <c r="S74" s="20"/>
-    </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75" s="1"/>
       <c r="B75" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>68</v>
       </c>
-      <c r="C75" s="24" t="s">
+      <c r="C75" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="D75" s="21" t="s">
+      <c r="D75" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="E75" s="21" t="s">
+      <c r="E75" s="20" t="s">
         <v>168</v>
       </c>
-      <c r="F75" s="21" t="s">
-        <v>417</v>
-      </c>
-      <c r="G75" s="21" t="s">
+      <c r="F75" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="G75" s="20" t="s">
         <v>211</v>
       </c>
-      <c r="H75" s="21" t="s">
+      <c r="H75" s="20" t="s">
         <v>290</v>
       </c>
-      <c r="I75" s="21"/>
-      <c r="J75" s="21" t="s">
-        <v>395</v>
+      <c r="I75" s="20"/>
+      <c r="J75" s="20" t="s">
+        <v>394</v>
       </c>
       <c r="K75" s="14" t="s">
-        <v>397</v>
-      </c>
-      <c r="L75" s="21">
+        <v>396</v>
+      </c>
+      <c r="L75" s="20">
         <v>2</v>
       </c>
       <c r="M75" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
-      <c r="N75" s="21">
+      <c r="N75" s="20">
         <v>21</v>
       </c>
-      <c r="O75" s="51" t="s">
-        <v>403</v>
-      </c>
-      <c r="P75" s="22">
+      <c r="O75" s="43" t="s">
+        <v>402</v>
+      </c>
+      <c r="P75" s="21">
         <v>0.33029999999999998</v>
       </c>
-      <c r="Q75" s="22">
-        <f>P75*N75</f>
+      <c r="Q75" s="21">
+        <f t="shared" si="3"/>
         <v>6.9362999999999992</v>
       </c>
-      <c r="R75" s="21"/>
-      <c r="S75" s="21"/>
-    </row>
-    <row r="76" spans="1:19" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R75" s="20"/>
+    </row>
+    <row r="76" spans="1:18" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
       <c r="B76" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>69</v>
       </c>
-      <c r="C76" s="24" t="s">
+      <c r="C76" s="23" t="s">
+        <v>417</v>
+      </c>
+      <c r="D76" s="20" t="s">
+        <v>396</v>
+      </c>
+      <c r="E76" s="20" t="s">
+        <v>422</v>
+      </c>
+      <c r="F76" s="20" t="s">
+        <v>396</v>
+      </c>
+      <c r="G76" s="20" t="s">
+        <v>423</v>
+      </c>
+      <c r="H76" s="20" t="s">
+        <v>424</v>
+      </c>
+      <c r="I76" s="20"/>
+      <c r="J76" s="20" t="s">
+        <v>396</v>
+      </c>
+      <c r="K76" s="14" t="s">
+        <v>396</v>
+      </c>
+      <c r="L76" s="20">
+        <v>1</v>
+      </c>
+      <c r="M76" s="14">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="N76" s="20">
+        <v>10</v>
+      </c>
+      <c r="O76" s="43" t="s">
+        <v>424</v>
+      </c>
+      <c r="P76" s="21">
+        <v>127.46</v>
+      </c>
+      <c r="Q76" s="21">
+        <f t="shared" si="3"/>
+        <v>1274.5999999999999</v>
+      </c>
+      <c r="R76" s="51" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="1"/>
+      <c r="B77" s="17">
+        <f t="shared" si="1"/>
+        <v>70</v>
+      </c>
+      <c r="C77" s="23" t="s">
+        <v>417</v>
+      </c>
+      <c r="D77" s="20" t="s">
+        <v>396</v>
+      </c>
+      <c r="E77" s="20" t="s">
         <v>418</v>
       </c>
-      <c r="D76" s="21" t="s">
-        <v>397</v>
-      </c>
-      <c r="E76" s="21" t="s">
+      <c r="F77" s="20" t="s">
+        <v>396</v>
+      </c>
+      <c r="G77" s="20" t="s">
         <v>419</v>
       </c>
-      <c r="F76" s="21" t="s">
-        <v>397</v>
-      </c>
-      <c r="G76" s="21" t="s">
+      <c r="H77" s="20"/>
+      <c r="I77" s="20"/>
+      <c r="J77" s="20" t="s">
+        <v>396</v>
+      </c>
+      <c r="K77" s="14" t="s">
+        <v>396</v>
+      </c>
+      <c r="L77" s="20">
+        <v>1</v>
+      </c>
+      <c r="M77" s="14">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="N77" s="20">
+        <v>10</v>
+      </c>
+      <c r="O77" s="43" t="s">
         <v>420</v>
       </c>
-      <c r="H76" s="21"/>
-      <c r="I76" s="21"/>
-      <c r="J76" s="21" t="s">
-        <v>397</v>
-      </c>
-      <c r="K76" s="14" t="s">
-        <v>397</v>
-      </c>
-      <c r="L76" s="21">
-        <v>1</v>
-      </c>
-      <c r="M76" s="14">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-      <c r="N76" s="21">
-        <v>10</v>
-      </c>
-      <c r="O76" s="51" t="s">
-        <v>421</v>
-      </c>
-      <c r="P76" s="22">
+      <c r="P77" s="21">
         <v>7.01</v>
       </c>
-      <c r="Q76" s="22">
-        <f>P76*N76</f>
+      <c r="Q77" s="21">
+        <f t="shared" si="3"/>
         <v>70.099999999999994</v>
       </c>
-      <c r="R76" s="21"/>
-      <c r="S76" s="21"/>
-    </row>
-    <row r="77" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="1"/>
-      <c r="B77" s="1"/>
-      <c r="C77" s="1"/>
-      <c r="D77" s="1"/>
-      <c r="E77" s="1"/>
-      <c r="F77" s="1"/>
-      <c r="G77" s="1"/>
-      <c r="H77" s="1"/>
-      <c r="I77" s="1"/>
-      <c r="J77" s="1"/>
-      <c r="K77" s="1"/>
-      <c r="L77" s="1"/>
-      <c r="M77" s="1"/>
-      <c r="N77" s="45" t="s">
-        <v>3</v>
-      </c>
-      <c r="O77" s="46"/>
-      <c r="P77" s="46"/>
-      <c r="Q77" s="18">
-        <f>SUM(Q8:Q76)</f>
-        <v>697.26904999999999</v>
-      </c>
-      <c r="R77" s="1"/>
-      <c r="S77" s="1"/>
-    </row>
-    <row r="78" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R77" s="20"/>
+    </row>
+    <row r="78" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -6238,27 +6080,50 @@
       <c r="K78" s="1"/>
       <c r="L78" s="1"/>
       <c r="M78" s="1"/>
-      <c r="N78" s="45" t="s">
+      <c r="N78" s="49" t="s">
+        <v>3</v>
+      </c>
+      <c r="O78" s="50"/>
+      <c r="P78" s="50"/>
+      <c r="Q78" s="18">
+        <f>SUM(Q8:Q77)</f>
+        <v>1971.8690499999998</v>
+      </c>
+      <c r="R78" s="1"/>
+    </row>
+    <row r="79" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="1"/>
+      <c r="B79" s="1"/>
+      <c r="C79" s="1"/>
+      <c r="D79" s="1"/>
+      <c r="E79" s="1"/>
+      <c r="F79" s="1"/>
+      <c r="G79" s="1"/>
+      <c r="H79" s="1"/>
+      <c r="I79" s="1"/>
+      <c r="J79" s="1"/>
+      <c r="K79" s="1"/>
+      <c r="L79" s="1"/>
+      <c r="M79" s="1"/>
+      <c r="N79" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="O78" s="46"/>
-      <c r="P78" s="46"/>
-      <c r="Q78" s="19">
-        <f>Q77/10</f>
-        <v>69.726905000000002</v>
-      </c>
-      <c r="R78" s="1"/>
-      <c r="S78" s="1"/>
-    </row>
-    <row r="90" spans="13:13" x14ac:dyDescent="0.25">
-      <c r="M90" s="39"/>
+      <c r="O79" s="50"/>
+      <c r="P79" s="50"/>
+      <c r="Q79" s="19">
+        <f>Q78/10</f>
+        <v>197.18690499999997</v>
+      </c>
+      <c r="R79" s="1"/>
+    </row>
+    <row r="91" spans="13:13" x14ac:dyDescent="0.25">
+      <c r="M91" s="38"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="K1:S1"/>
-    <mergeCell ref="N77:P77"/>
+  <mergeCells count="3">
+    <mergeCell ref="K1:R1"/>
     <mergeCell ref="N78:P78"/>
-    <mergeCell ref="S2:S6"/>
+    <mergeCell ref="N79:P79"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O14" r:id="rId1"/>
@@ -6326,12 +6191,12 @@
     <hyperlink ref="O54" r:id="rId63"/>
     <hyperlink ref="O55" r:id="rId64"/>
     <hyperlink ref="O59" r:id="rId65"/>
-    <hyperlink ref="O76" r:id="rId66"/>
+    <hyperlink ref="O77" r:id="rId66"/>
     <hyperlink ref="O63" r:id="rId67"/>
     <hyperlink ref="O71" r:id="rId68"/>
+    <hyperlink ref="O76" r:id="rId69"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId69"/>
-  <drawing r:id="rId70"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId70"/>
 </worksheet>
 </file>